--- a/GOOG.xlsx
+++ b/GOOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D541C3B80E9AE39F/Documente/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{0BE00285-ED23-EC41-8344-E6516A943060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6036AD3F-E6BF-884C-8CEE-F5BB806C4321}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AFD872-E9E3-4998-A09A-0DEDD0E34018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14660" yWindow="500" windowWidth="14140" windowHeight="15600" activeTab="1" xr2:uid="{5B77E953-101E-4842-99C5-2529E3ADE585}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5B77E953-101E-4842-99C5-2529E3ADE585}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="150">
   <si>
     <t>Revenue</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Debt</t>
   </si>
   <si>
-    <t>EV</t>
-  </si>
-  <si>
     <t>Gross Margin</t>
   </si>
   <si>
@@ -433,6 +430,63 @@
   </si>
   <si>
     <t>Revenue Growth y/y</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Sundar Pichai</t>
+  </si>
+  <si>
+    <t>since 2019</t>
+  </si>
+  <si>
+    <t>CFO</t>
+  </si>
+  <si>
+    <t>Anat Ashkenazi</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Name Company</t>
+  </si>
+  <si>
+    <t>Value in millions</t>
+  </si>
+  <si>
+    <t>Undisclosed</t>
+  </si>
+  <si>
+    <t>Wiz-Cloud Security</t>
+  </si>
+  <si>
+    <t>Intersect-Energy/AI</t>
+  </si>
+  <si>
+    <t>Cameyo-Virtualization</t>
+  </si>
+  <si>
+    <t>Photomath-AI Education</t>
+  </si>
+  <si>
+    <t>Mandiant-Cybersecurity</t>
+  </si>
+  <si>
+    <t>Raxium-Hardware</t>
+  </si>
+  <si>
+    <t>Fitbit-Wearables</t>
+  </si>
+  <si>
+    <t>Looker-Data Analytics</t>
+  </si>
+  <si>
+    <t>HTC-Hardware</t>
+  </si>
+  <si>
+    <t>Apigee-API Management</t>
   </si>
 </sst>
 </file>
@@ -442,7 +496,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ _R_O_N;[Red]\-#,##0\ _R_O_N"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -478,20 +532,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -503,6 +543,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -516,6 +557,15 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -555,7 +605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -566,13 +616,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -580,18 +627,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -607,6 +666,120 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF7BFB7F-8A97-5290-0ED5-3D1C20C949EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12306300" y="0"/>
+          <a:ext cx="2438400" cy="2171700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2" descr="Logo Design History of Amazon: What Changed in 30 years?">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AABC218-0935-4C7C-8048-B365EDF529D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7172325" y="3686175"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -851,10 +1024,6 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'0'0</inkml:trace>
 </inkml:ink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1174,22 +1343,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCD14D6-3051-8D42-AA77-1B5B5C734215}">
-  <dimension ref="A2:I60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:J40"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
     <col min="3" max="3" width="57.5" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
@@ -1200,12 +1372,12 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
@@ -1219,12 +1391,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
         <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
@@ -1236,12 +1408,12 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
         <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>92</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
@@ -1255,12 +1427,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s">
         <v>93</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
@@ -1270,332 +1442,398 @@
         <f>10886+6116</f>
         <v>17002</v>
       </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="3">
-        <f>H5+H7-H6</f>
-        <v>2067080</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="14"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="G9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="26">
+        <v>1998</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="17"/>
+      <c r="C10" s="15" t="s">
+        <v>100</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1998</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="15" t="s">
         <v>101</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="17" t="s">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="17" t="s">
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="15" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="17" t="s">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B15" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="G14" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C15" s="16"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="23">
+        <v>2025</v>
+      </c>
+      <c r="I16" t="s">
+        <v>140</v>
+      </c>
+      <c r="J16" s="24">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C16" s="19"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="15" t="s">
+      <c r="G17" s="2"/>
+      <c r="H17" s="23">
+        <v>2025</v>
+      </c>
+      <c r="I17" t="s">
+        <v>141</v>
+      </c>
+      <c r="J17" s="24">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15" t="s">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="23">
+        <v>2024</v>
+      </c>
+      <c r="I18" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15" t="s">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="23">
+        <v>2023</v>
+      </c>
+      <c r="I19" t="s">
+        <v>143</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="23">
+        <v>2022</v>
+      </c>
+      <c r="I20" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20" s="24">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="23">
+        <v>2022</v>
+      </c>
+      <c r="I21" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="24">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B27" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15" t="s">
+      <c r="C22" s="12"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="23">
+        <v>2021</v>
+      </c>
+      <c r="I22" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="24">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="15"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15" t="s">
+      <c r="C23" s="12"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="23">
+        <v>2019</v>
+      </c>
+      <c r="I23" t="s">
+        <v>147</v>
+      </c>
+      <c r="J23" s="24">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="15"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15" t="s">
+      <c r="C24" s="12"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="23">
+        <v>2017</v>
+      </c>
+      <c r="I24" t="s">
+        <v>148</v>
+      </c>
+      <c r="J24" s="24">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="15"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15" t="s">
+      <c r="C25" s="12"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="23">
+        <v>2016</v>
+      </c>
+      <c r="I25" t="s">
+        <v>149</v>
+      </c>
+      <c r="J25" s="24">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="23"/>
+      <c r="J26" s="24"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" s="25"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="15"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B39" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B41" s="15" t="s">
+      <c r="C28" s="12"/>
+      <c r="J28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="15"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B43" s="15" t="s">
+      <c r="C29" s="12"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="15"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B45" s="15" t="s">
+      <c r="C30" s="12"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="15"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B47" s="15" t="s">
+      <c r="C31" s="12"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="15"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="15" t="s">
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B55" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-    </row>
-    <row r="56" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="15"/>
-    </row>
-    <row r="57" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-    </row>
-    <row r="58" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-    </row>
-    <row r="59" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-    </row>
-    <row r="60" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC29AFE5-0412-BE46-AA05-FD560F72645D}">
-  <dimension ref="B1:BX80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:BX80"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.6640625" customWidth="1"/>
-    <col min="46" max="46" width="18.1640625" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="1"/>
+    <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="21" width="11.5" style="1"/>
+    <col min="22" max="23" width="10.625" style="1" customWidth="1"/>
+    <col min="24" max="45" width="11.5" style="1"/>
+    <col min="46" max="46" width="18.125" style="1" customWidth="1"/>
+    <col min="47" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:76" x14ac:dyDescent="0.2">
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-    </row>
     <row r="2" spans="2:76" x14ac:dyDescent="0.2">
-      <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1668,8 +1906,6 @@
       <c r="Z2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
       <c r="AC2" s="1">
         <v>2020</v>
       </c>
@@ -1857,7 +2093,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="3" spans="2:76" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:76" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1929,19 +2165,18 @@
       <c r="W3" s="5">
         <v>90234</v>
       </c>
-      <c r="X3" s="21">
+      <c r="X3" s="5">
         <f>96428</f>
         <v>96428</v>
       </c>
-      <c r="Y3" s="21">
+      <c r="Y3" s="5">
         <f>X3*1.06</f>
         <v>102213.68000000001</v>
       </c>
-      <c r="Z3" s="21">
+      <c r="Z3" s="5">
         <f>Y3*1.06</f>
         <v>108346.50080000001</v>
       </c>
-      <c r="AB3" s="1"/>
       <c r="AC3" s="3">
         <f>SUM(C3:F3)</f>
         <v>182527</v>
@@ -2006,15 +2241,15 @@
         <f t="shared" si="2"/>
         <v>779363.43518315174</v>
       </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2"/>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
-      <c r="AX3" s="2"/>
-      <c r="AY3" s="2"/>
-      <c r="AZ3" s="2"/>
-      <c r="BA3" s="2"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="AZ3" s="3"/>
+      <c r="BA3" s="3"/>
     </row>
     <row r="4" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -2099,7 +2334,6 @@
         <f t="shared" si="3"/>
         <v>43864.220400000006</v>
       </c>
-      <c r="AB4" s="1"/>
       <c r="AC4" s="3">
         <f>SUM(C4:F4)</f>
         <v>84732</v>
@@ -2164,15 +2398,15 @@
         <f t="shared" si="5"/>
         <v>286929.20527973876</v>
       </c>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="3"/>
+      <c r="BA4" s="3"/>
     </row>
     <row r="5" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -2274,7 +2508,6 @@
         <f t="shared" si="7"/>
         <v>64482.280400000003</v>
       </c>
-      <c r="AB5" s="1"/>
       <c r="AC5" s="3">
         <f t="shared" ref="AC5:AG5" si="8">AC3-AC4</f>
         <v>97795</v>
@@ -2339,15 +2572,15 @@
         <f t="shared" si="9"/>
         <v>492434.22990341298</v>
       </c>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
+      <c r="AS5" s="3"/>
+      <c r="AT5" s="3"/>
+      <c r="AU5" s="3"/>
+      <c r="AV5" s="3"/>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+      <c r="AZ5" s="3"/>
+      <c r="BA5" s="3"/>
     </row>
     <row r="6" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
@@ -2432,7 +2665,6 @@
         <f t="shared" si="10"/>
         <v>14932.569600000001</v>
       </c>
-      <c r="AB6" s="1"/>
       <c r="AC6" s="3">
         <f>SUM(C6:F6)</f>
         <v>27573</v>
@@ -2497,15 +2729,15 @@
         <f t="shared" si="12"/>
         <v>117659.60472571681</v>
       </c>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="AZ6" s="3"/>
+      <c r="BA6" s="3"/>
     </row>
     <row r="7" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
@@ -2589,7 +2821,6 @@
         <f t="shared" si="13"/>
         <v>8436.6981000000014</v>
       </c>
-      <c r="AB7" s="1"/>
       <c r="AC7" s="3">
         <f>SUM(C7:F7)</f>
         <v>17946</v>
@@ -2653,15 +2884,15 @@
         <f t="shared" si="14"/>
         <v>47970.601595824242</v>
       </c>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
+      <c r="AU7" s="3"/>
+      <c r="AV7" s="3"/>
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+      <c r="AZ7" s="3"/>
+      <c r="BA7" s="3"/>
     </row>
     <row r="8" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -2745,7 +2976,6 @@
         <f t="shared" si="15"/>
         <v>5634.0544000000009</v>
       </c>
-      <c r="AB8" s="1"/>
       <c r="AC8" s="3">
         <f>SUM(C8:F8)</f>
         <v>11052</v>
@@ -2810,15 +3040,15 @@
         <f t="shared" si="16"/>
         <v>32251.159729499919</v>
       </c>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2"/>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2"/>
-      <c r="BA8" s="2"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="AZ8" s="3"/>
+      <c r="BA8" s="3"/>
     </row>
     <row r="9" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
@@ -2920,7 +3150,6 @@
         <f t="shared" si="18"/>
         <v>29003.322100000005</v>
       </c>
-      <c r="AB9" s="1"/>
       <c r="AC9" s="3">
         <f t="shared" ref="AC9:AH9" si="19">SUM(AC6:AC8)</f>
         <v>56571</v>
@@ -2985,15 +3214,15 @@
         <f t="shared" si="20"/>
         <v>197881.36605104097</v>
       </c>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="AY9" s="2"/>
-      <c r="AZ9" s="2"/>
-      <c r="BA9" s="2"/>
+      <c r="AS9" s="3"/>
+      <c r="AT9" s="3"/>
+      <c r="AU9" s="3"/>
+      <c r="AV9" s="3"/>
+      <c r="AW9" s="3"/>
+      <c r="AX9" s="3"/>
+      <c r="AY9" s="3"/>
+      <c r="AZ9" s="3"/>
+      <c r="BA9" s="3"/>
     </row>
     <row r="10" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
@@ -3095,7 +3324,6 @@
         <f t="shared" si="22"/>
         <v>35478.958299999998</v>
       </c>
-      <c r="AB10" s="1"/>
       <c r="AC10" s="3">
         <f t="shared" ref="AC10:AG10" si="23">AC5-AC9</f>
         <v>41224</v>
@@ -3160,15 +3388,15 @@
         <f t="shared" si="24"/>
         <v>294552.86385237204</v>
       </c>
-      <c r="AS10" s="2"/>
-      <c r="AT10" s="2"/>
-      <c r="AU10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
-      <c r="AX10" s="2"/>
-      <c r="AY10" s="2"/>
-      <c r="AZ10" s="2"/>
-      <c r="BA10" s="2"/>
+      <c r="AS10" s="3"/>
+      <c r="AT10" s="3"/>
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="3"/>
+      <c r="AW10" s="3"/>
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="3"/>
+      <c r="AZ10" s="3"/>
+      <c r="BA10" s="3"/>
     </row>
     <row r="11" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
@@ -3250,7 +3478,6 @@
         <f t="shared" si="25"/>
         <v>2688.62</v>
       </c>
-      <c r="AB11" s="1"/>
       <c r="AC11" s="3">
         <f>SUM(C11:F11)</f>
         <v>6858</v>
@@ -3315,15 +3542,15 @@
         <f t="shared" si="26"/>
         <v>5910.4132366676995</v>
       </c>
-      <c r="AS11" s="2"/>
-      <c r="AT11" s="2"/>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2"/>
-      <c r="BA11" s="2"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="3"/>
+      <c r="AW11" s="3"/>
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+      <c r="AZ11" s="3"/>
+      <c r="BA11" s="3"/>
     </row>
     <row r="12" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
@@ -3425,7 +3652,6 @@
         <f t="shared" si="28"/>
         <v>38167.578300000001</v>
       </c>
-      <c r="AB12" s="1"/>
       <c r="AC12" s="3">
         <f t="shared" ref="AC12:AF12" si="29">SUM(AC10:AC11)</f>
         <v>48082</v>
@@ -3490,15 +3716,15 @@
         <f t="shared" si="30"/>
         <v>300463.27708903974</v>
       </c>
-      <c r="AS12" s="2"/>
-      <c r="AT12" s="2"/>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2"/>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2"/>
-      <c r="BA12" s="2"/>
+      <c r="AS12" s="3"/>
+      <c r="AT12" s="3"/>
+      <c r="AU12" s="3"/>
+      <c r="AV12" s="3"/>
+      <c r="AW12" s="3"/>
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="3"/>
+      <c r="AZ12" s="3"/>
+      <c r="BA12" s="3"/>
     </row>
     <row r="13" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
@@ -3581,7 +3807,6 @@
       <c r="Z13" s="3">
         <v>7249</v>
       </c>
-      <c r="AB13" s="1"/>
       <c r="AC13" s="3">
         <f>SUM(C13:F13)</f>
         <v>7813</v>
@@ -3646,15 +3871,15 @@
         <f t="shared" si="31"/>
         <v>17715</v>
       </c>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="AY13" s="2"/>
-      <c r="AZ13" s="2"/>
-      <c r="BA13" s="2"/>
+      <c r="AS13" s="3"/>
+      <c r="AT13" s="3"/>
+      <c r="AU13" s="3"/>
+      <c r="AV13" s="3"/>
+      <c r="AW13" s="3"/>
+      <c r="AX13" s="3"/>
+      <c r="AY13" s="3"/>
+      <c r="AZ13" s="3"/>
+      <c r="BA13" s="3"/>
     </row>
     <row r="14" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -3756,7 +3981,6 @@
         <f t="shared" si="33"/>
         <v>30918.578300000001</v>
       </c>
-      <c r="AB14" s="1"/>
       <c r="AC14" s="3">
         <f t="shared" ref="AC14:AG14" si="34">AC12-AC13</f>
         <v>40269</v>
@@ -3821,131 +4045,131 @@
         <f t="shared" si="35"/>
         <v>282748.27708903974</v>
       </c>
-      <c r="AS14" s="2">
+      <c r="AS14" s="3">
         <f>+AR14*(1+$AT$25)</f>
         <v>279920.79431814933</v>
       </c>
-      <c r="AT14" s="2">
+      <c r="AT14" s="3">
         <f t="shared" ref="AT14:BX14" si="36">+AS14*(1+$AT$25)</f>
         <v>277121.58637496782</v>
       </c>
-      <c r="AU14" s="2">
+      <c r="AU14" s="3">
         <f t="shared" si="36"/>
         <v>274350.37051121815</v>
       </c>
-      <c r="AV14" s="2">
+      <c r="AV14" s="3">
         <f t="shared" si="36"/>
         <v>271606.86680610594</v>
       </c>
-      <c r="AW14" s="2">
+      <c r="AW14" s="3">
         <f t="shared" si="36"/>
         <v>268890.79813804489</v>
       </c>
-      <c r="AX14" s="2">
+      <c r="AX14" s="3">
         <f t="shared" si="36"/>
         <v>266201.89015666442</v>
       </c>
-      <c r="AY14" s="2">
+      <c r="AY14" s="3">
         <f t="shared" si="36"/>
         <v>263539.87125509779</v>
       </c>
-      <c r="AZ14" s="2">
+      <c r="AZ14" s="3">
         <f t="shared" si="36"/>
         <v>260904.47254254681</v>
       </c>
-      <c r="BA14" s="2">
+      <c r="BA14" s="3">
         <f t="shared" si="36"/>
         <v>258295.42781712132</v>
       </c>
-      <c r="BB14" s="2">
+      <c r="BB14" s="3">
         <f t="shared" si="36"/>
         <v>255712.47353895011</v>
       </c>
-      <c r="BC14" s="2">
+      <c r="BC14" s="3">
         <f t="shared" si="36"/>
         <v>253155.3488035606</v>
       </c>
-      <c r="BD14" s="2">
+      <c r="BD14" s="3">
         <f t="shared" si="36"/>
         <v>250623.795315525</v>
       </c>
-      <c r="BE14" s="2">
+      <c r="BE14" s="3">
         <f t="shared" si="36"/>
         <v>248117.55736236976</v>
       </c>
-      <c r="BF14" s="2">
+      <c r="BF14" s="3">
         <f t="shared" si="36"/>
         <v>245636.38178874605</v>
       </c>
-      <c r="BG14" s="2">
+      <c r="BG14" s="3">
         <f t="shared" si="36"/>
         <v>243180.01797085858</v>
       </c>
-      <c r="BH14" s="2">
+      <c r="BH14" s="3">
         <f t="shared" si="36"/>
         <v>240748.21779115</v>
       </c>
-      <c r="BI14" s="2">
+      <c r="BI14" s="3">
         <f t="shared" si="36"/>
         <v>238340.7356132385</v>
       </c>
-      <c r="BJ14" s="2">
+      <c r="BJ14" s="3">
         <f t="shared" si="36"/>
         <v>235957.32825710613</v>
       </c>
-      <c r="BK14" s="2">
+      <c r="BK14" s="3">
         <f t="shared" si="36"/>
         <v>233597.75497453506</v>
       </c>
-      <c r="BL14" s="2">
+      <c r="BL14" s="3">
         <f t="shared" si="36"/>
         <v>231261.7774247897</v>
       </c>
-      <c r="BM14" s="2">
+      <c r="BM14" s="3">
         <f t="shared" si="36"/>
         <v>228949.15965054181</v>
       </c>
-      <c r="BN14" s="2">
+      <c r="BN14" s="3">
         <f t="shared" si="36"/>
         <v>226659.66805403639</v>
       </c>
-      <c r="BO14" s="2">
+      <c r="BO14" s="3">
         <f t="shared" si="36"/>
         <v>224393.07137349603</v>
       </c>
-      <c r="BP14" s="2">
+      <c r="BP14" s="3">
         <f t="shared" si="36"/>
         <v>222149.14065976106</v>
       </c>
-      <c r="BQ14" s="2">
+      <c r="BQ14" s="3">
         <f t="shared" si="36"/>
         <v>219927.64925316346</v>
       </c>
-      <c r="BR14" s="2">
+      <c r="BR14" s="3">
         <f t="shared" si="36"/>
         <v>217728.37276063181</v>
       </c>
-      <c r="BS14" s="2">
+      <c r="BS14" s="3">
         <f t="shared" si="36"/>
         <v>215551.08903302549</v>
       </c>
-      <c r="BT14" s="2">
+      <c r="BT14" s="3">
         <f t="shared" si="36"/>
         <v>213395.57814269525</v>
       </c>
-      <c r="BU14" s="2">
+      <c r="BU14" s="3">
         <f t="shared" si="36"/>
         <v>211261.6223612683</v>
       </c>
-      <c r="BV14" s="2">
+      <c r="BV14" s="3">
         <f t="shared" si="36"/>
         <v>209149.00613765561</v>
       </c>
-      <c r="BW14" s="2">
+      <c r="BW14" s="3">
         <f t="shared" si="36"/>
         <v>207057.51607627905</v>
       </c>
-      <c r="BX14" s="2">
+      <c r="BX14" s="3">
         <f t="shared" si="36"/>
         <v>204986.94091551626</v>
       </c>
@@ -4042,7 +4266,6 @@
       <c r="Z15" s="3">
         <v>12135</v>
       </c>
-      <c r="AB15" s="1"/>
       <c r="AC15" s="3">
         <v>687</v>
       </c>
@@ -4092,7 +4315,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="16" spans="2:76" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:76" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>12</v>
       </c>
@@ -4192,7 +4415,6 @@
         <f t="shared" si="38"/>
         <v>2.547884491141327</v>
       </c>
-      <c r="AB16" s="1"/>
       <c r="AC16" s="9">
         <f t="shared" ref="AC16:AG16" si="39">AC14/AC15</f>
         <v>58.615720524017469</v>
@@ -4259,7 +4481,6 @@
       </c>
     </row>
     <row r="17" spans="2:47" x14ac:dyDescent="0.2">
-      <c r="B17" s="1"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -4281,16 +4502,6 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1"/>
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
@@ -4299,10 +4510,10 @@
     </row>
     <row r="18" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C18" s="6">
-        <f t="shared" ref="C18:W18" si="41">C5/C3</f>
+        <f t="shared" ref="C18:V18" si="41">C5/C3</f>
         <v>0.53881289632887097</v>
       </c>
       <c r="D18" s="6">
@@ -4397,7 +4608,6 @@
         <f t="shared" si="42"/>
         <v>0.5951487119923673</v>
       </c>
-      <c r="AB18" s="1"/>
       <c r="AC18" s="6">
         <f t="shared" ref="AC18:AH18" si="43">AC5/AC3</f>
         <v>0.53578374706207854</v>
@@ -4465,7 +4675,7 @@
     </row>
     <row r="19" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="6">
         <f t="shared" ref="C19:V19" si="45">C13/C12</f>
@@ -4556,14 +4766,13 @@
         <v>0.16905849418005009</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" ref="X19:Z19" si="46">Y13/Y12</f>
+        <f t="shared" ref="Y19:Z19" si="46">Y13/Y12</f>
         <v>0.21757889823856841</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="46"/>
         <v>0.18992559451957683</v>
       </c>
-      <c r="AB19" s="1"/>
       <c r="AC19" s="6">
         <f t="shared" ref="AC19:AF19" si="47">AC13/AC12</f>
         <v>0.16249324071378063</v>
@@ -4629,9 +4838,9 @@
         <v>5.8958952227464091E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:47" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -4780,4315 +4989,4313 @@
       </c>
     </row>
     <row r="21" spans="2:47" x14ac:dyDescent="0.2">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="3"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="3"/>
+      <c r="AM21" s="3"/>
     </row>
     <row r="22" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="2">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3">
         <f t="shared" ref="C22:W22" si="53">C23-C41</f>
         <v>124580</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <f t="shared" si="53"/>
         <v>130023</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="3">
         <f t="shared" si="53"/>
         <v>133350</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <f t="shared" si="53"/>
         <v>143465</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <f t="shared" si="53"/>
         <v>146511</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="3">
         <f t="shared" si="53"/>
         <v>147067</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="3">
         <f t="shared" si="53"/>
         <v>153816</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="3">
         <f t="shared" si="53"/>
         <v>154381</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="3">
         <f t="shared" si="53"/>
         <v>149723</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22" s="3">
         <f t="shared" si="53"/>
         <v>140928</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" s="3">
         <f t="shared" si="53"/>
         <v>132025</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" s="3">
         <f t="shared" si="53"/>
         <v>129553</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" s="3">
         <f t="shared" si="53"/>
         <v>132618</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="3">
         <f t="shared" si="53"/>
         <v>135851</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="3">
         <f t="shared" si="53"/>
         <v>137061</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" s="3">
         <f t="shared" si="53"/>
         <v>128671</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22" s="3">
         <f t="shared" si="53"/>
         <v>128846</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T22" s="3">
         <f t="shared" si="53"/>
         <v>121659</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="3">
         <f t="shared" si="53"/>
         <v>117110</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V22" s="3">
         <f t="shared" si="53"/>
         <v>122756</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W22" s="3">
         <f t="shared" si="53"/>
         <v>135471</v>
       </c>
-      <c r="AI22" s="2"/>
-      <c r="AJ22" s="2"/>
-      <c r="AK22" s="2"/>
-      <c r="AL22" s="2"/>
-      <c r="AM22" s="2"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3"/>
     </row>
     <row r="23" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <f>117229+12367</f>
         <v>129596</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <f>121080+12961</f>
         <v>134041</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="3">
         <f>20129+112467+14656</f>
         <v>147252</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <f>26465+110229+20703</f>
         <v>157397</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="3">
         <f>108482+26622+25294</f>
         <v>160398</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="3">
         <f>23630+112233+25532</f>
         <v>161395</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="3">
         <f>23719+118284+26101</f>
         <v>168104</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="3">
         <f>20945+118704+29549</f>
         <v>169198</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="3">
         <f>113084+20886+30544</f>
         <v>164514</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="3">
         <f>17936+107061+30665</f>
         <v>155662</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="3">
         <f>21984+94275+30419</f>
         <v>146678</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="3">
         <f>21879+91883+30492</f>
         <v>144254</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23" s="3">
         <f>89178+25924+31213</f>
         <v>146315</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="3">
         <f>25929+92403+31224</f>
         <v>149556</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="3">
         <f>30702+89233+30907</f>
         <v>150842</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R23" s="3">
         <f>24048+86868+31008</f>
         <v>141924</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23" s="3">
         <f>24493+83597+33994</f>
         <v>142084</v>
       </c>
-      <c r="T23" s="2">
+      <c r="T23" s="3">
         <f>27225+73500+34172</f>
         <v>134897</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="3">
         <f>93230+36177</f>
         <v>129407</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23" s="3">
         <f>95657+37982</f>
         <v>133639</v>
       </c>
-      <c r="W23" s="2">
+      <c r="W23" s="3">
         <f>95328+51029</f>
         <v>146357</v>
       </c>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
-      <c r="AL23" s="2"/>
-      <c r="AM23" s="2"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="3"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="3"/>
     </row>
     <row r="24" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="2">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3">
         <v>21825</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>21201</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="3">
         <v>24925</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>30930</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="3">
         <v>28006</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="3">
         <v>31967</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="3">
         <v>34047</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="3">
         <v>39304</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24" s="3">
         <v>34703</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="3">
         <v>35707</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="3">
         <v>34697</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="3">
         <v>40258</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" s="3">
         <v>36036</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="3">
         <v>38804</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="3">
         <v>41020</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" s="3">
         <v>47964</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="3">
         <v>44552</v>
       </c>
-      <c r="T24" s="2">
+      <c r="T24" s="3">
         <v>47087</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="3">
         <v>49104</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" s="3">
         <v>52340</v>
       </c>
-      <c r="W24" s="2">
+      <c r="W24" s="3">
         <v>51000</v>
       </c>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-    </row>
-    <row r="25" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="3"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="3"/>
+    </row>
+    <row r="25" spans="2:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>1910</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>394</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="3">
         <v>588</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>454</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="3">
         <v>493</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="3">
         <v>884</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="3">
         <v>753</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="3">
         <v>966</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" s="3">
         <v>919</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="3">
         <v>1366</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" s="3">
         <v>1479</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R25" s="3">
         <v>0</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S25" s="3">
         <v>0</v>
       </c>
-      <c r="T25" s="2">
+      <c r="T25" s="3">
         <v>0</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="3">
         <v>0</v>
       </c>
-      <c r="V25" s="2">
+      <c r="V25" s="3">
         <v>0</v>
       </c>
-      <c r="W25" s="2">
+      <c r="W25" s="3">
         <v>0</v>
       </c>
-      <c r="AI25" s="2"/>
-      <c r="AJ25" s="2"/>
-      <c r="AK25" s="2"/>
-      <c r="AL25" s="2"/>
-      <c r="AM25" s="2"/>
-      <c r="AS25" s="12" t="s">
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AS25" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT25" s="17">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="26" spans="2:47" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="3">
+        <v>889</v>
+      </c>
+      <c r="D26" s="3">
+        <v>815</v>
+      </c>
+      <c r="E26" s="3">
+        <v>835</v>
+      </c>
+      <c r="F26" s="3">
+        <v>728</v>
+      </c>
+      <c r="G26" s="3">
+        <v>888</v>
+      </c>
+      <c r="H26" s="3">
+        <v>907</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1278</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1170</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1369</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1980</v>
+      </c>
+      <c r="M26" s="3">
+        <v>3156</v>
+      </c>
+      <c r="N26" s="3">
+        <v>2670</v>
+      </c>
+      <c r="O26" s="3">
+        <v>2315</v>
+      </c>
+      <c r="P26" s="3">
+        <v>2231</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>2957</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="3"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="3"/>
+      <c r="AS26" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AT25" s="24">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="26" spans="2:47" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="2">
-        <v>889</v>
-      </c>
-      <c r="D26" s="2">
-        <v>815</v>
-      </c>
-      <c r="E26" s="2">
-        <v>835</v>
-      </c>
-      <c r="F26" s="2">
-        <v>728</v>
-      </c>
-      <c r="G26" s="2">
-        <v>888</v>
-      </c>
-      <c r="H26" s="2">
-        <v>907</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1278</v>
-      </c>
-      <c r="J26" s="11">
-        <v>1170</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1369</v>
-      </c>
-      <c r="L26" s="2">
-        <v>1980</v>
-      </c>
-      <c r="M26" s="2">
-        <v>3156</v>
-      </c>
-      <c r="N26" s="2">
-        <v>2670</v>
-      </c>
-      <c r="O26" s="2">
-        <v>2315</v>
-      </c>
-      <c r="P26" s="2">
-        <v>2231</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>2957</v>
-      </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
-        <v>0</v>
-      </c>
-      <c r="T26" s="2">
-        <v>0</v>
-      </c>
-      <c r="U26" s="2">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2">
-        <v>0</v>
-      </c>
-      <c r="W26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="2"/>
-      <c r="AJ26" s="2"/>
-      <c r="AK26" s="2"/>
-      <c r="AL26" s="2"/>
-      <c r="AM26" s="2"/>
-      <c r="AS26" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="AT26" s="24">
+      <c r="AT26" s="17">
         <v>0.05</v>
       </c>
-      <c r="AU26" s="20">
-        <v>0.01</v>
-      </c>
+      <c r="AU26" s="18"/>
     </row>
     <row r="27" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="2">
+        <v>47</v>
+      </c>
+      <c r="C27" s="3">
         <v>5165</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>5579</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="3">
         <v>5425</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>5490</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="3">
         <v>7646</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="3">
         <v>6076</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="3">
         <v>6029</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="3">
         <v>7054</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="3">
         <v>6892</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27" s="3">
         <v>8321</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27" s="3">
         <v>10518</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27" s="3">
         <v>8105</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27" s="3">
         <v>8532</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="3">
         <v>9421</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="3">
         <v>12398</v>
       </c>
-      <c r="R27" s="2">
+      <c r="R27" s="3">
         <v>12650</v>
       </c>
-      <c r="S27" s="2">
+      <c r="S27" s="3">
         <v>12829</v>
       </c>
-      <c r="T27" s="2">
+      <c r="T27" s="3">
         <v>14183</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="3">
         <v>15207</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" s="3">
         <v>15714</v>
       </c>
-      <c r="W27" s="2">
+      <c r="W27" s="3">
         <v>15724</v>
       </c>
-      <c r="AI27" s="2"/>
-      <c r="AJ27" s="2"/>
-      <c r="AK27" s="2"/>
-      <c r="AL27" s="2"/>
-      <c r="AM27" s="2"/>
-      <c r="AS27" t="s">
-        <v>126</v>
-      </c>
-      <c r="AT27" s="22">
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="3"/>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="3"/>
+      <c r="AM27" s="3"/>
+      <c r="AS27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT27" s="19">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="2">
+        <v>48</v>
+      </c>
+      <c r="C28" s="3">
         <f>730</f>
         <v>730</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>895</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="3">
         <v>972</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>1084</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="3">
         <v>1129</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="3">
         <v>1153</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="3">
         <v>1195</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="3">
         <v>1284</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K28" s="3">
         <v>1388</v>
       </c>
-      <c r="L28" s="2">
+      <c r="L28" s="3">
         <v>1490</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28" s="3">
         <v>2991</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="3">
         <v>5261</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28" s="3">
         <v>6885</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="3">
         <v>9357</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="3">
         <v>10983</v>
       </c>
-      <c r="R28" s="2">
+      <c r="R28" s="3">
         <v>12169</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" s="3">
         <v>11687</v>
       </c>
-      <c r="T28" s="2">
+      <c r="T28" s="3">
         <v>14958</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="3">
         <v>15915</v>
       </c>
-      <c r="V28" s="2">
+      <c r="V28" s="3">
         <v>17180</v>
       </c>
-      <c r="W28" s="2">
+      <c r="W28" s="3">
         <v>18386</v>
       </c>
-      <c r="AI28" s="2"/>
-      <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
-      <c r="AL28" s="2"/>
-      <c r="AM28" s="2"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="3"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="3"/>
     </row>
     <row r="29" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="2">
+        <v>49</v>
+      </c>
+      <c r="C29" s="3">
         <v>76747</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>78748</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="3">
         <v>81636</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>84749</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="3">
         <v>87606</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="3">
         <v>91697</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="3">
         <v>94631</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="3">
         <v>97599</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="3">
         <v>104218</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29" s="3">
         <v>106223</v>
       </c>
-      <c r="M29" s="2">
+      <c r="M29" s="3">
         <v>108363</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29" s="3">
         <v>112668</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O29" s="3">
         <v>117560</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="3">
         <v>121208</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="3">
         <v>125705</v>
       </c>
-      <c r="R29" s="2">
+      <c r="R29" s="3">
         <v>134345</v>
       </c>
-      <c r="S29" s="2">
+      <c r="S29" s="3">
         <v>143182</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T29" s="3">
         <v>151155</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="3">
         <v>161270</v>
       </c>
-      <c r="V29" s="2">
+      <c r="V29" s="3">
         <v>171036</v>
       </c>
-      <c r="W29" s="2">
+      <c r="W29" s="3">
         <v>185062</v>
       </c>
-      <c r="AI29" s="2"/>
-      <c r="AJ29" s="2"/>
-      <c r="AK29" s="2"/>
-      <c r="AL29" s="2"/>
-      <c r="AM29" s="2"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="3"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="3"/>
     </row>
     <row r="30" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="2">
+        <v>50</v>
+      </c>
+      <c r="C30" s="3">
         <v>11219</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>11567</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="3">
         <v>11946</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>12211</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="3">
         <v>12598</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="3">
         <v>12978</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="3">
         <v>12918</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="3">
         <v>12959</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30" s="3">
         <f>12992</f>
         <v>12992</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L30" s="3">
         <v>13398</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" s="3">
         <v>13677</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="3">
         <v>14381</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O30" s="3">
         <v>14447</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="3">
         <v>14469</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="3">
         <v>14199</v>
       </c>
-      <c r="R30" s="2">
+      <c r="R30" s="3">
         <v>14091</v>
       </c>
-      <c r="S30" s="2">
+      <c r="S30" s="3">
         <v>13768</v>
       </c>
-      <c r="T30" s="2">
+      <c r="T30" s="3">
         <v>13606</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="3">
         <v>13561</v>
       </c>
-      <c r="V30" s="2">
+      <c r="V30" s="3">
         <v>13588</v>
       </c>
-      <c r="W30" s="2">
+      <c r="W30" s="3">
         <v>13722</v>
       </c>
-      <c r="AI30" s="2"/>
-      <c r="AJ30" s="2"/>
-      <c r="AK30" s="2"/>
-      <c r="AL30" s="2"/>
-      <c r="AM30" s="2"/>
-      <c r="AS30" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT30" s="23">
+      <c r="AI30" s="3"/>
+      <c r="AJ30" s="3"/>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3"/>
+      <c r="AM30" s="3"/>
+      <c r="AS30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AT30" s="20">
         <f>NPV(AT26,AF14:BX14)</f>
         <v>3767108.1385483732</v>
       </c>
     </row>
     <row r="31" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="2">
+        <v>51</v>
+      </c>
+      <c r="C31" s="3">
         <f>20737+1840</f>
         <v>22577</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <f>20824+1697</f>
         <v>22521</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="3">
         <v>20870</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>21175</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <f>22341+1823</f>
         <v>24164</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="3">
         <f>22406+1626</f>
         <v>24032</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="3">
         <f>22623+1549</f>
         <v>24172</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="3">
         <f>22956+1417</f>
         <v>24373</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <f>23010+1313</f>
         <v>24323</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="3">
         <f>23949+1377</f>
         <v>25326</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="3">
         <f>28834+2192</f>
         <v>31026</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="3">
         <f>28960+2084</f>
         <v>31044</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31" s="3">
         <f>1968+28994</f>
         <v>30962</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="3">
         <f>29210+1966</f>
         <v>31176</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="3">
         <f>1833+29146</f>
         <v>30979</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="3">
         <f>29198</f>
         <v>29198</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" s="3">
         <v>29183</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T31" s="3">
         <v>29185</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="3">
         <v>31935</v>
       </c>
-      <c r="V31" s="2">
+      <c r="V31" s="3">
         <v>31885</v>
       </c>
-      <c r="W31" s="2">
+      <c r="W31" s="3">
         <v>32173</v>
       </c>
-      <c r="AI31" s="2"/>
-      <c r="AJ31" s="2"/>
-      <c r="AK31" s="2"/>
-      <c r="AL31" s="2"/>
-      <c r="AM31" s="2"/>
-      <c r="AS31" t="s">
-        <v>128</v>
-      </c>
-      <c r="AT31" s="2">
+      <c r="AI31" s="3"/>
+      <c r="AJ31" s="3"/>
+      <c r="AK31" s="3"/>
+      <c r="AL31" s="3"/>
+      <c r="AM31" s="3"/>
+      <c r="AS31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT31" s="3">
         <f>+AT30/Main!H4</f>
         <v>310.43330354745558</v>
       </c>
     </row>
     <row r="32" spans="2:47" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2748</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2731</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3274</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3953</v>
+      </c>
+      <c r="G32" s="3">
+        <v>4167</v>
+      </c>
+      <c r="H32" s="3">
+        <v>4298</v>
+      </c>
+      <c r="I32" s="3">
+        <v>4276</v>
+      </c>
+      <c r="J32" s="3">
+        <v>5361</v>
+      </c>
+      <c r="K32" s="3">
+        <v>5778</v>
+      </c>
+      <c r="L32" s="3">
+        <v>5712</v>
+      </c>
+      <c r="M32" s="3">
+        <v>5670</v>
+      </c>
+      <c r="N32" s="3">
+        <v>6623</v>
+      </c>
+      <c r="O32" s="3">
+        <v>6439</v>
+      </c>
+      <c r="P32" s="3">
+        <v>6822</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>7628</v>
+      </c>
+      <c r="R32" s="3">
+        <v>10051</v>
+      </c>
+      <c r="S32" s="3">
+        <v>10065</v>
+      </c>
+      <c r="T32" s="3">
+        <v>9699</v>
+      </c>
+      <c r="U32" s="3">
+        <v>13867</v>
+      </c>
+      <c r="V32" s="3">
+        <v>14874</v>
+      </c>
+      <c r="W32" s="3">
+        <v>12950</v>
+      </c>
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="3"/>
+      <c r="AK32" s="3"/>
+      <c r="AL32" s="3"/>
+      <c r="AM32" s="3"/>
+      <c r="AS32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT32" s="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="33" spans="2:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="2">
-        <v>2748</v>
-      </c>
-      <c r="D32" s="2">
-        <v>2731</v>
-      </c>
-      <c r="E32" s="2">
-        <v>3274</v>
-      </c>
-      <c r="F32" s="2">
-        <v>3953</v>
-      </c>
-      <c r="G32" s="2">
-        <v>4167</v>
-      </c>
-      <c r="H32" s="2">
-        <v>4298</v>
-      </c>
-      <c r="I32" s="2">
-        <v>4276</v>
-      </c>
-      <c r="J32" s="2">
-        <v>5361</v>
-      </c>
-      <c r="K32" s="2">
-        <v>5778</v>
-      </c>
-      <c r="L32" s="2">
-        <v>5712</v>
-      </c>
-      <c r="M32" s="2">
-        <v>5670</v>
-      </c>
-      <c r="N32" s="2">
-        <v>6623</v>
-      </c>
-      <c r="O32" s="2">
-        <v>6439</v>
-      </c>
-      <c r="P32" s="2">
-        <v>6822</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>7628</v>
-      </c>
-      <c r="R32" s="2">
-        <v>10051</v>
-      </c>
-      <c r="S32" s="2">
-        <v>10065</v>
-      </c>
-      <c r="T32" s="2">
-        <v>9699</v>
-      </c>
-      <c r="U32" s="2">
-        <v>13867</v>
-      </c>
-      <c r="V32" s="2">
-        <v>14874</v>
-      </c>
-      <c r="W32" s="2">
-        <v>12950</v>
-      </c>
-      <c r="AI32" s="2"/>
-      <c r="AJ32" s="2"/>
-      <c r="AK32" s="2"/>
-      <c r="AL32" s="2"/>
-      <c r="AM32" s="2"/>
-      <c r="AS32" t="s">
-        <v>129</v>
-      </c>
-      <c r="AT32">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="33" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="B33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="C33" s="3">
         <f t="shared" ref="C33:W33" si="54">SUM(C23:C32)</f>
         <v>273406</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
         <f t="shared" si="54"/>
         <v>278492</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="3">
         <f t="shared" si="54"/>
         <v>297723</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <f t="shared" si="54"/>
         <v>318171</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="3">
         <f t="shared" si="54"/>
         <v>327095</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="3">
         <f t="shared" si="54"/>
         <v>335387</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="3">
         <f t="shared" si="54"/>
         <v>347403</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="3">
         <f t="shared" si="54"/>
         <v>359268</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" s="3">
         <f t="shared" si="54"/>
         <v>357096</v>
       </c>
-      <c r="L33" s="2">
+      <c r="L33" s="3">
         <f t="shared" si="54"/>
         <v>355185</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33" s="3">
         <f t="shared" si="54"/>
         <v>358255</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33" s="3">
         <f t="shared" si="54"/>
         <v>365264</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O33" s="3">
         <f t="shared" si="54"/>
         <v>369491</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="3">
         <f t="shared" si="54"/>
         <v>383044</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="3">
         <f t="shared" si="54"/>
         <v>396711</v>
       </c>
-      <c r="R33" s="2">
+      <c r="R33" s="3">
         <f t="shared" si="54"/>
         <v>402392</v>
       </c>
-      <c r="S33" s="2">
+      <c r="S33" s="3">
         <f t="shared" si="54"/>
         <v>407350</v>
       </c>
-      <c r="T33" s="2">
+      <c r="T33" s="3">
         <f t="shared" si="54"/>
         <v>414770</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="3">
         <f t="shared" si="54"/>
         <v>430266</v>
       </c>
-      <c r="V33" s="2">
+      <c r="V33" s="3">
         <f t="shared" si="54"/>
         <v>450256</v>
       </c>
-      <c r="W33" s="2">
+      <c r="W33" s="3">
         <f t="shared" si="54"/>
         <v>475374</v>
       </c>
-      <c r="AI33" s="2"/>
-      <c r="AJ33" s="2"/>
-      <c r="AK33" s="2"/>
-      <c r="AL33" s="2"/>
-      <c r="AM33" s="2"/>
-      <c r="AS33" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT33" s="25">
+      <c r="AI33" s="3"/>
+      <c r="AJ33" s="3"/>
+      <c r="AK33" s="3"/>
+      <c r="AL33" s="3"/>
+      <c r="AM33" s="3"/>
+      <c r="AS33" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AT33" s="8">
         <f>AT31/AT32-1</f>
         <v>0.53679853241314635</v>
       </c>
     </row>
     <row r="34" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="AI34" s="2"/>
-      <c r="AJ34" s="2"/>
-      <c r="AK34" s="2"/>
-      <c r="AL34" s="2"/>
-      <c r="AM34" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="AI34" s="3"/>
+      <c r="AJ34" s="3"/>
+      <c r="AK34" s="3"/>
+      <c r="AL34" s="3"/>
+      <c r="AM34" s="3"/>
     </row>
     <row r="35" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="2">
+        <v>54</v>
+      </c>
+      <c r="C35" s="3">
         <v>4099</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="3">
         <v>4064</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="3">
         <v>4391</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>5589</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="3">
         <v>4801</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="3">
         <v>4708</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="3">
         <v>4616</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="3">
         <v>6037</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35" s="3">
         <v>3436</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="3">
         <v>4409</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="3">
         <v>6303</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="3">
         <v>5128</v>
       </c>
-      <c r="O35" s="2">
+      <c r="O35" s="3">
         <v>4184</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="3">
         <v>5313</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="3">
         <v>5803</v>
       </c>
-      <c r="R35" s="2">
+      <c r="R35" s="3">
         <v>7493</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S35" s="3">
         <v>6198</v>
       </c>
-      <c r="T35" s="2">
+      <c r="T35" s="3">
         <v>6092</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="3">
         <v>7049</v>
       </c>
-      <c r="V35" s="2">
+      <c r="V35" s="3">
         <v>7987</v>
       </c>
-      <c r="W35" s="2">
+      <c r="W35" s="3">
         <v>8497</v>
       </c>
-      <c r="AI35" s="2"/>
-      <c r="AJ35" s="2"/>
-      <c r="AK35" s="2"/>
-      <c r="AL35" s="2"/>
-      <c r="AM35" s="2"/>
+      <c r="AI35" s="3"/>
+      <c r="AJ35" s="3"/>
+      <c r="AK35" s="3"/>
+      <c r="AL35" s="3"/>
+      <c r="AM35" s="3"/>
     </row>
     <row r="36" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="2">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3">
         <v>5656</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>7127</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="3">
         <v>8747</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>11086</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>8375</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="3">
         <v>10088</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="3">
         <v>12170</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="3">
         <v>13889</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36" s="3">
         <v>9803</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="3">
         <v>10852</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36" s="3">
         <v>12366</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N36" s="3">
         <v>14028</v>
       </c>
-      <c r="O36" s="2">
+      <c r="O36" s="3">
         <v>9954</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="3">
         <v>11260</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="3">
         <v>12562</v>
       </c>
-      <c r="R36" s="2">
+      <c r="R36" s="3">
         <v>15140</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S36" s="3">
         <v>9703</v>
       </c>
-      <c r="T36" s="2">
+      <c r="T36" s="3">
         <v>11373</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="3">
         <v>12908</v>
       </c>
-      <c r="V36" s="2">
+      <c r="V36" s="3">
         <v>15069</v>
       </c>
-      <c r="W36" s="2">
+      <c r="W36" s="3">
         <v>9984</v>
       </c>
-      <c r="AI36" s="2"/>
-      <c r="AJ36" s="2"/>
-      <c r="AK36" s="2"/>
-      <c r="AL36" s="2"/>
-      <c r="AM36" s="2"/>
+      <c r="AI36" s="3"/>
+      <c r="AJ36" s="3"/>
+      <c r="AK36" s="3"/>
+      <c r="AL36" s="3"/>
+      <c r="AM36" s="3"/>
     </row>
     <row r="37" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="2">
+        <v>56</v>
+      </c>
+      <c r="C37" s="3">
         <v>22601</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>24426</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="3">
         <v>25631</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>28631</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="3">
         <v>30732</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="3">
         <v>28891</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="3">
         <v>30113</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="3">
         <v>31236</v>
       </c>
-      <c r="K37" s="2">
+      <c r="K37" s="3">
         <v>33051</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37" s="3">
         <v>32976</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37" s="3">
         <v>35038</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37" s="3">
         <v>37866</v>
       </c>
-      <c r="O37" s="2">
+      <c r="O37" s="3">
         <v>43185</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="3">
         <v>49300</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="3">
         <v>55602</v>
       </c>
-      <c r="R37" s="2">
+      <c r="R37" s="3">
         <v>46168</v>
       </c>
-      <c r="S37" s="2">
+      <c r="S37" s="3">
         <v>48603</v>
       </c>
-      <c r="T37" s="2">
+      <c r="T37" s="3">
         <v>47298</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="3">
         <v>46585</v>
       </c>
-      <c r="V37" s="2">
+      <c r="V37" s="3">
         <v>51228</v>
       </c>
-      <c r="W37" s="2">
+      <c r="W37" s="3">
         <v>58300</v>
       </c>
-      <c r="AI37" s="2"/>
-      <c r="AJ37" s="2"/>
-      <c r="AK37" s="2"/>
-      <c r="AL37" s="2"/>
-      <c r="AM37" s="2"/>
+      <c r="AI37" s="3"/>
+      <c r="AJ37" s="3"/>
+      <c r="AK37" s="3"/>
+      <c r="AL37" s="3"/>
+      <c r="AM37" s="3"/>
     </row>
     <row r="38" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="2">
+        <v>57</v>
+      </c>
+      <c r="C38" s="3">
         <v>4982</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>5005</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="3">
         <v>6030</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>7500</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="3">
         <v>6962</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="3">
         <v>7438</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="3">
         <v>7745</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="3">
         <v>8996</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="3">
         <v>8116</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="3">
         <v>7889</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38" s="3">
         <v>7662</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N38" s="3">
         <v>8370</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O38" s="3">
         <v>7816</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="3">
         <v>7990</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="3">
         <v>8025</v>
       </c>
-      <c r="R38" s="2">
+      <c r="R38" s="3">
         <v>8876</v>
       </c>
-      <c r="S38" s="2">
+      <c r="S38" s="3">
         <v>8520</v>
       </c>
-      <c r="T38" s="2">
+      <c r="T38" s="3">
         <v>8899</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="3">
         <v>9365</v>
       </c>
-      <c r="V38" s="2">
+      <c r="V38" s="3">
         <v>9802</v>
       </c>
-      <c r="W38" s="2">
+      <c r="W38" s="3">
         <v>9965</v>
       </c>
-      <c r="AI38" s="2"/>
-      <c r="AJ38" s="2"/>
-      <c r="AK38" s="2"/>
-      <c r="AL38" s="2"/>
-      <c r="AM38" s="2"/>
+      <c r="AI38" s="3"/>
+      <c r="AJ38" s="3"/>
+      <c r="AK38" s="3"/>
+      <c r="AL38" s="3"/>
+      <c r="AM38" s="3"/>
     </row>
     <row r="39" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="2">
+        <v>58</v>
+      </c>
+      <c r="C39" s="3">
         <v>1939</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>2061</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="3">
         <v>2302</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>2543</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="3">
         <f>2690+530+4406</f>
         <v>7626</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="3">
         <f>2715+510+4703</f>
         <v>7928</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I39" s="3">
         <f>2968+510+3551</f>
         <v>7029</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="3">
         <f>3288+535+5257</f>
         <v>9080</v>
       </c>
-      <c r="K39" s="2">
+      <c r="K39" s="3">
         <f>3198+499+2843</f>
         <v>6540</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="4">
         <f>3272+472+924</f>
         <v>4668</v>
       </c>
-      <c r="M39" s="2">
+      <c r="M39" s="3">
         <f>476+594+3585</f>
         <v>4655</v>
       </c>
-      <c r="N39" s="2">
+      <c r="N39" s="3">
         <f>3908+599</f>
         <v>4507</v>
       </c>
-      <c r="O39" s="2">
+      <c r="O39" s="3">
         <f>3715+610</f>
         <v>4325</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="3">
         <f>3846+667</f>
         <v>4513</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="3">
         <f>4303+884</f>
         <v>5187</v>
       </c>
-      <c r="R39" s="2">
+      <c r="R39" s="3">
         <f>4137+911</f>
         <v>5048</v>
       </c>
-      <c r="S39" s="2">
+      <c r="S39" s="3">
         <f>3973+921</f>
         <v>4894</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T39" s="3">
         <f>4251+985</f>
         <v>5236</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="3">
         <f>4896+1015</f>
         <v>5911</v>
       </c>
-      <c r="V39" s="2">
+      <c r="V39" s="3">
         <v>5036</v>
       </c>
-      <c r="W39" s="2">
+      <c r="W39" s="3">
         <v>4908</v>
       </c>
-      <c r="AI39" s="2"/>
-      <c r="AJ39" s="2"/>
-      <c r="AK39" s="2"/>
-      <c r="AL39" s="2"/>
-      <c r="AM39" s="2"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
     <row r="40" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <f>9207+2079+913</f>
         <v>12199</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
         <f>975+8599</f>
         <v>9574</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="3">
         <f>1099+8616</f>
         <v>9715</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <f>1485+8849+3561+481</f>
         <v>14376</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="3">
         <f>1893+9278</f>
         <v>11171</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="3">
         <f>1811+8651</f>
         <v>10462</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I40" s="3">
         <f>4170+8984</f>
         <v>13154</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="3">
         <f>808+9176</f>
         <v>9984</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K40" s="3">
         <f>4344+9406</f>
         <v>13750</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L40" s="3">
         <f>1956+8163</f>
         <v>10119</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M40" s="3">
         <f>1025+8572</f>
         <v>9597</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40" s="3">
         <f>9258+514</f>
         <v>9772</v>
       </c>
-      <c r="O40" s="2">
+      <c r="O40" s="3">
         <f>9722+542</f>
         <v>10264</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="3">
         <f>8753+558</f>
         <v>9311</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="3">
         <f>8038+528</f>
         <v>8566</v>
       </c>
-      <c r="R40" s="2">
+      <c r="R40" s="3">
         <f>485+8474</f>
         <v>8959</v>
       </c>
-      <c r="S40" s="2">
+      <c r="S40" s="3">
         <f>9234+486</f>
         <v>9720</v>
       </c>
-      <c r="T40" s="2">
+      <c r="T40" s="3">
         <f>7703+717</f>
         <v>8420</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="3">
         <f>8219+706</f>
         <v>8925</v>
       </c>
-      <c r="V40" s="2">
+      <c r="V40" s="3">
         <f>8782</f>
         <v>8782</v>
       </c>
-      <c r="W40" s="2">
+      <c r="W40" s="3">
         <v>9773</v>
       </c>
-      <c r="AI40" s="2"/>
-      <c r="AJ40" s="2"/>
-      <c r="AK40" s="2"/>
-      <c r="AL40" s="2"/>
-      <c r="AM40" s="2"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
     <row r="41" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <v>5016</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>4018</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="3">
         <v>13902</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="3">
         <v>13932</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="3">
         <v>13887</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="3">
         <v>14328</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I41" s="3">
         <v>14288</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="3">
         <v>14817</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="3">
         <v>14791</v>
       </c>
-      <c r="L41" s="2">
+      <c r="L41" s="3">
         <v>14734</v>
       </c>
-      <c r="M41" s="2">
+      <c r="M41" s="3">
         <v>14653</v>
       </c>
-      <c r="N41" s="2">
+      <c r="N41" s="3">
         <v>14701</v>
       </c>
-      <c r="O41" s="2">
+      <c r="O41" s="3">
         <v>13697</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="3">
         <v>13705</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="3">
         <v>13781</v>
       </c>
-      <c r="R41" s="2">
+      <c r="R41" s="3">
         <v>13253</v>
       </c>
-      <c r="S41" s="2">
+      <c r="S41" s="3">
         <v>13238</v>
       </c>
-      <c r="T41" s="2">
+      <c r="T41" s="3">
         <v>13238</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="3">
         <v>12297</v>
       </c>
-      <c r="V41" s="2">
+      <c r="V41" s="3">
         <v>10883</v>
       </c>
-      <c r="W41" s="2">
+      <c r="W41" s="3">
         <v>10886</v>
       </c>
-      <c r="AI41" s="2"/>
-      <c r="AJ41" s="2"/>
-      <c r="AK41" s="2"/>
-      <c r="AL41" s="2"/>
-      <c r="AM41" s="2"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="3"/>
+      <c r="AK41" s="3"/>
+      <c r="AL41" s="3"/>
+      <c r="AM41" s="3"/>
     </row>
     <row r="42" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="2">
+        <v>50</v>
+      </c>
+      <c r="C42" s="3">
         <v>10476</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>10709</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="3">
         <v>10984</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>11146</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="3">
         <v>11382</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="3">
         <v>11619</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I42" s="3">
         <v>11471</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="3">
         <v>11389</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42" s="3">
         <v>11363</v>
       </c>
-      <c r="L42" s="2">
+      <c r="L42" s="3">
         <v>11697</v>
       </c>
-      <c r="M42" s="2">
+      <c r="M42" s="3">
         <v>11984</v>
       </c>
-      <c r="N42" s="2">
+      <c r="N42" s="3">
         <v>12501</v>
       </c>
-      <c r="O42" s="2">
+      <c r="O42" s="3">
         <v>12799</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="3">
         <v>12746</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="3">
         <v>12550</v>
       </c>
-      <c r="R42" s="2">
+      <c r="R42" s="3">
         <v>12460</v>
       </c>
-      <c r="S42" s="2">
+      <c r="S42" s="3">
         <v>11957</v>
       </c>
-      <c r="T42" s="2">
+      <c r="T42" s="3">
         <v>11708</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="3">
         <v>11654</v>
       </c>
-      <c r="V42" s="2">
+      <c r="V42" s="3">
         <v>11691</v>
       </c>
-      <c r="W42" s="2">
+      <c r="W42" s="3">
         <v>11678</v>
       </c>
-      <c r="AI42" s="2"/>
-      <c r="AJ42" s="2"/>
-      <c r="AK42" s="2"/>
-      <c r="AL42" s="2"/>
-      <c r="AM42" s="2"/>
+      <c r="AI42" s="3"/>
+      <c r="AJ42" s="3"/>
+      <c r="AK42" s="3"/>
+      <c r="AL42" s="3"/>
+      <c r="AM42" s="3"/>
     </row>
     <row r="43" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="2">
+        <v>59</v>
+      </c>
+      <c r="C43" s="3">
         <v>2427</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>1992</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="3">
         <v>2194</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>2269</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="3">
         <v>2146</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="3">
         <v>2270</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I43" s="3">
         <v>2250</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="3">
         <v>2205</v>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="3">
         <v>2242</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L43" s="3">
         <v>2422</v>
       </c>
-      <c r="M43" s="2">
+      <c r="M43" s="3">
         <v>2371</v>
       </c>
-      <c r="N43" s="2">
+      <c r="N43" s="3">
         <v>2247</v>
       </c>
-      <c r="O43" s="2">
+      <c r="O43" s="3">
         <v>2373</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="3">
         <v>1765</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="3">
         <v>1433</v>
       </c>
-      <c r="R43" s="2">
+      <c r="R43" s="3">
         <v>1616</v>
       </c>
-      <c r="S43" s="2">
+      <c r="S43" s="3">
         <v>1683</v>
       </c>
-      <c r="T43" s="2">
+      <c r="T43" s="3">
         <v>1753</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="3">
         <v>1453</v>
       </c>
-      <c r="V43" s="2">
+      <c r="V43" s="3">
         <v>4694</v>
       </c>
-      <c r="W43" s="2">
+      <c r="W43" s="3">
         <v>6116</v>
       </c>
-      <c r="AI43" s="2"/>
-      <c r="AJ43" s="2"/>
-      <c r="AK43" s="2"/>
-      <c r="AL43" s="2"/>
-      <c r="AM43" s="2"/>
+      <c r="AI43" s="3"/>
+      <c r="AJ43" s="3"/>
+      <c r="AK43" s="3"/>
+      <c r="AL43" s="3"/>
+      <c r="AM43" s="3"/>
     </row>
     <row r="44" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="2">
+        <v>60</v>
+      </c>
+      <c r="C44" s="3">
         <v>203659</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>207322</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="3">
         <v>212920</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>222544</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="3">
         <v>230013</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="3">
         <v>237565</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I44" s="3">
         <v>244567</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="3">
         <v>251635</v>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="3">
         <v>254004</v>
       </c>
-      <c r="L44" s="2">
+      <c r="L44" s="3">
         <v>255419</v>
       </c>
-      <c r="M44" s="2">
+      <c r="M44" s="3">
         <v>253626</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="3">
         <v>256144</v>
       </c>
-      <c r="O44" s="2">
+      <c r="O44" s="3">
         <v>260894</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="3">
         <v>267141</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="3">
         <v>273202</v>
       </c>
-      <c r="R44" s="2">
+      <c r="R44" s="3">
         <v>283379</v>
       </c>
-      <c r="S44" s="2">
+      <c r="S44" s="3">
         <v>292844</v>
       </c>
-      <c r="T44" s="2">
+      <c r="T44" s="3">
         <v>300753</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="3">
         <v>314119</v>
       </c>
-      <c r="V44" s="2">
+      <c r="V44" s="3">
         <v>325084</v>
       </c>
-      <c r="W44" s="2">
+      <c r="W44" s="3">
         <v>345267</v>
       </c>
-      <c r="AI44" s="2"/>
-      <c r="AJ44" s="2"/>
-      <c r="AK44" s="2"/>
-      <c r="AL44" s="2"/>
-      <c r="AM44" s="2"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="3"/>
+      <c r="AK44" s="3"/>
+      <c r="AL44" s="3"/>
+      <c r="AM44" s="3"/>
     </row>
     <row r="45" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="2">
+        <v>61</v>
+      </c>
+      <c r="C45" s="3">
         <f>SUM(C35:C44)</f>
         <v>273054</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <f t="shared" ref="D45:W45" si="55">SUM(D35:D44)</f>
         <v>276298</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="3">
         <f t="shared" si="55"/>
         <v>296816</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <f t="shared" si="55"/>
         <v>319616</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="3">
         <f t="shared" si="55"/>
         <v>327095</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="3">
         <f t="shared" si="55"/>
         <v>335297</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I45" s="3">
         <f t="shared" si="55"/>
         <v>347403</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="3">
         <f t="shared" si="55"/>
         <v>359268</v>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="3">
         <f t="shared" si="55"/>
         <v>357096</v>
       </c>
-      <c r="L45" s="2">
+      <c r="L45" s="3">
         <f t="shared" si="55"/>
         <v>355185</v>
       </c>
-      <c r="M45" s="2">
+      <c r="M45" s="3">
         <f t="shared" si="55"/>
         <v>358255</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="3">
         <f t="shared" si="55"/>
         <v>365264</v>
       </c>
-      <c r="O45" s="2">
+      <c r="O45" s="3">
         <f t="shared" si="55"/>
         <v>369491</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="3">
         <f t="shared" si="55"/>
         <v>383044</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="3">
         <f t="shared" si="55"/>
         <v>396711</v>
       </c>
-      <c r="R45" s="2">
+      <c r="R45" s="3">
         <f t="shared" si="55"/>
         <v>402392</v>
       </c>
-      <c r="S45" s="2">
+      <c r="S45" s="3">
         <f t="shared" si="55"/>
         <v>407360</v>
       </c>
-      <c r="T45" s="2">
+      <c r="T45" s="3">
         <f t="shared" si="55"/>
         <v>414770</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="3">
         <f t="shared" si="55"/>
         <v>430266</v>
       </c>
-      <c r="V45" s="2">
+      <c r="V45" s="3">
         <f t="shared" si="55"/>
         <v>450256</v>
       </c>
-      <c r="W45" s="2">
+      <c r="W45" s="3">
         <f t="shared" si="55"/>
         <v>475374</v>
       </c>
-      <c r="AI45" s="2"/>
-      <c r="AJ45" s="2"/>
-      <c r="AK45" s="2"/>
-      <c r="AL45" s="2"/>
-      <c r="AM45" s="2"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="3"/>
+      <c r="AK45" s="3"/>
+      <c r="AL45" s="3"/>
+      <c r="AM45" s="3"/>
     </row>
     <row r="46" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="AI46" s="2"/>
-      <c r="AJ46" s="2"/>
-      <c r="AK46" s="2"/>
-      <c r="AL46" s="2"/>
-      <c r="AM46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="AI46" s="3"/>
+      <c r="AJ46" s="3"/>
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="3"/>
+      <c r="AM46" s="3"/>
     </row>
     <row r="47" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="2">
+        <v>62</v>
+      </c>
+      <c r="C47" s="3">
         <f t="shared" ref="C47:W47" si="56">+C14</f>
         <v>6836</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <f t="shared" si="56"/>
         <v>6959</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="3">
         <f t="shared" si="56"/>
         <v>11247</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <f t="shared" si="56"/>
         <v>15227</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="3">
         <f t="shared" si="56"/>
         <v>17930</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="3">
         <f t="shared" si="56"/>
         <v>18525</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="3">
         <f t="shared" si="56"/>
         <v>18936</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="3">
         <f t="shared" ref="J47" si="57">+J14</f>
         <v>20642</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="3">
         <f t="shared" si="56"/>
         <v>16436</v>
       </c>
-      <c r="L47" s="2">
+      <c r="L47" s="3">
         <f t="shared" si="56"/>
         <v>16002</v>
       </c>
-      <c r="M47" s="2">
+      <c r="M47" s="3">
         <f t="shared" si="56"/>
         <v>13910</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="3">
         <f t="shared" si="56"/>
         <v>11537</v>
       </c>
-      <c r="O47" s="2">
+      <c r="O47" s="3">
         <f t="shared" si="56"/>
         <v>15051</v>
       </c>
-      <c r="P47" s="2">
+      <c r="P47" s="3">
         <f t="shared" si="56"/>
         <v>18368</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47" s="3">
         <f t="shared" si="56"/>
         <v>19689</v>
       </c>
-      <c r="R47" s="2">
+      <c r="R47" s="3">
         <f t="shared" si="56"/>
         <v>20687</v>
       </c>
-      <c r="S47" s="2">
+      <c r="S47" s="3">
         <v>23662</v>
       </c>
-      <c r="T47" s="2">
+      <c r="T47" s="3">
         <f t="shared" si="56"/>
         <v>23619</v>
       </c>
-      <c r="U47" s="2">
+      <c r="U47" s="3">
         <f t="shared" si="56"/>
         <v>23116</v>
       </c>
-      <c r="V47" s="2">
+      <c r="V47" s="3">
         <f t="shared" si="56"/>
         <v>26603</v>
       </c>
-      <c r="W47" s="2">
+      <c r="W47" s="3">
         <f t="shared" si="56"/>
         <v>23357</v>
       </c>
-      <c r="AI47" s="2"/>
-      <c r="AJ47" s="2"/>
-      <c r="AK47" s="2"/>
-      <c r="AL47" s="2"/>
-      <c r="AM47" s="2"/>
+      <c r="AI47" s="3"/>
+      <c r="AJ47" s="3"/>
+      <c r="AK47" s="3"/>
+      <c r="AL47" s="3"/>
+      <c r="AM47" s="3"/>
     </row>
     <row r="48" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="2">
+        <v>63</v>
+      </c>
+      <c r="C48" s="3">
         <v>6836</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>6959</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="3">
         <v>11247</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="3">
         <f>34343-SUM(C48:E48)</f>
         <v>9301</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="3">
         <v>17930</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="3">
         <v>18525</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="3">
         <v>18936</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="3">
         <f>76033-SUM(G48:I48)</f>
         <v>20642</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K48" s="3">
         <v>16436</v>
       </c>
-      <c r="L48" s="2">
+      <c r="L48" s="3">
         <v>16002</v>
       </c>
-      <c r="M48" s="2">
+      <c r="M48" s="3">
         <v>13910</v>
       </c>
-      <c r="N48" s="2">
+      <c r="N48" s="3">
         <f>59972-SUM(K48:M48)</f>
         <v>13624</v>
       </c>
-      <c r="O48" s="2">
+      <c r="O48" s="3">
         <v>15051</v>
       </c>
-      <c r="P48" s="2">
+      <c r="P48" s="3">
         <v>18368</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48" s="3">
         <v>19689</v>
       </c>
-      <c r="R48" s="2">
+      <c r="R48" s="3">
         <v>20687</v>
       </c>
-      <c r="S48" s="2">
+      <c r="S48" s="3">
         <v>23662</v>
       </c>
-      <c r="T48" s="2">
+      <c r="T48" s="3">
         <v>23619</v>
       </c>
-      <c r="U48" s="2">
+      <c r="U48" s="3">
         <v>26301</v>
       </c>
-      <c r="V48" s="2">
+      <c r="V48" s="3">
         <f>100118-SUM(S48:U48)</f>
         <v>26536</v>
       </c>
-      <c r="W48" s="2">
+      <c r="W48" s="3">
         <v>34540</v>
       </c>
-      <c r="AI48" s="2"/>
-      <c r="AJ48" s="2"/>
-      <c r="AK48" s="2"/>
-      <c r="AL48" s="2"/>
-      <c r="AM48" s="2"/>
+      <c r="AI48" s="3"/>
+      <c r="AJ48" s="3"/>
+      <c r="AK48" s="3"/>
+      <c r="AL48" s="3"/>
+      <c r="AM48" s="3"/>
     </row>
     <row r="49" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="2">
+        <v>64</v>
+      </c>
+      <c r="C49" s="3">
         <v>2899</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <f>6077-C49</f>
         <v>3178</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="3">
         <f>9366-SUM(C49:D49)</f>
         <v>3289</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <f>12905-SUM(C49:E49)</f>
         <v>3539</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="3">
         <v>2525</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="3">
         <f>5255-G49</f>
         <v>2730</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="3">
         <f>8340-SUM(G49:H49)</f>
         <v>3085</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="3">
         <f>11555-SUM(G49:I49)</f>
         <v>3215</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="3">
         <f>3591</f>
         <v>3591</v>
       </c>
-      <c r="L49" s="2">
+      <c r="L49" s="3">
         <f>7289-K49</f>
         <v>3698</v>
       </c>
-      <c r="M49" s="2">
+      <c r="M49" s="3">
         <f>11222-SUM(K49:L49)</f>
         <v>3933</v>
       </c>
-      <c r="N49" s="2">
+      <c r="N49" s="3">
         <f>15287-SUM(K49:M49)</f>
         <v>4065</v>
       </c>
-      <c r="O49" s="2">
+      <c r="O49" s="3">
         <v>3060</v>
       </c>
-      <c r="P49" s="2">
+      <c r="P49" s="3">
         <f>6339-O49</f>
         <v>3279</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49" s="3">
         <f>10010-SUM(O49:P49)</f>
         <v>3671</v>
       </c>
-      <c r="R49" s="2">
+      <c r="R49" s="3">
         <f>11946-SUM(O49:Q49)</f>
         <v>1936</v>
       </c>
-      <c r="S49" s="2">
+      <c r="S49" s="3">
         <v>3413</v>
       </c>
-      <c r="T49" s="2">
+      <c r="T49" s="3">
         <f>7121-S49</f>
         <v>3708</v>
       </c>
-      <c r="U49" s="2">
+      <c r="U49" s="3">
         <f>11106-SUM(S49:T49)</f>
         <v>3985</v>
       </c>
-      <c r="V49" s="2">
+      <c r="V49" s="3">
         <f>15311-SUM(S49:U49)</f>
         <v>4205</v>
       </c>
-      <c r="W49" s="2">
+      <c r="W49" s="3">
         <v>4487</v>
       </c>
-      <c r="AI49" s="2"/>
-      <c r="AJ49" s="2"/>
-      <c r="AK49" s="2"/>
-      <c r="AL49" s="2"/>
-      <c r="AM49" s="2"/>
+      <c r="AI49" s="3"/>
+      <c r="AJ49" s="3"/>
+      <c r="AK49" s="3"/>
+      <c r="AL49" s="3"/>
+      <c r="AM49" s="3"/>
     </row>
     <row r="50" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C50" s="2">
+        <v>65</v>
+      </c>
+      <c r="C50" s="3">
         <v>209</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <f>417-C50</f>
         <v>208</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="3">
         <f>606-SUM(C50:D50)</f>
         <v>189</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="3">
         <f>792-SUM(C50:E50)</f>
         <v>186</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="3">
         <v>228</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="3">
         <f>443-G50</f>
         <v>215</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="3">
         <f>662-SUM(G50:H50)</f>
         <v>219</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="3">
         <f>856-SUM(G50:I50)</f>
         <v>194</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50" s="3">
         <v>191</v>
       </c>
-      <c r="L50" s="2">
+      <c r="L50" s="3">
         <f>392-K50</f>
         <v>201</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M50" s="3">
         <f>505-SUM(K50:L50)</f>
         <v>113</v>
       </c>
-      <c r="N50" s="2">
+      <c r="N50" s="3">
         <f>641-SUM(K50:M50)</f>
         <v>136</v>
       </c>
-      <c r="O50" s="2">
+      <c r="O50" s="3">
         <v>126</v>
       </c>
-      <c r="P50" s="2">
+      <c r="P50" s="3">
         <f>244-O50</f>
         <v>118</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50" s="3">
         <f>373-SUM(O50:P50)</f>
         <v>129</v>
       </c>
-      <c r="R50" s="2">
+      <c r="R50" s="3">
         <v>0</v>
       </c>
-      <c r="S50" s="2">
+      <c r="S50" s="3">
         <v>0</v>
       </c>
-      <c r="T50" s="2">
+      <c r="T50" s="3">
         <v>0</v>
       </c>
-      <c r="U50" s="2">
+      <c r="U50" s="3">
         <v>0</v>
       </c>
-      <c r="V50" s="2">
+      <c r="V50" s="3">
         <v>0</v>
       </c>
-      <c r="W50" s="2">
+      <c r="W50" s="3">
         <v>0</v>
       </c>
-      <c r="AI50" s="2"/>
-      <c r="AJ50" s="2"/>
-      <c r="AK50" s="2"/>
-      <c r="AL50" s="2"/>
-      <c r="AM50" s="2"/>
+      <c r="AI50" s="3"/>
+      <c r="AJ50" s="3"/>
+      <c r="AK50" s="3"/>
+      <c r="AL50" s="3"/>
+      <c r="AM50" s="3"/>
     </row>
     <row r="51" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" s="2">
+        <v>66</v>
+      </c>
+      <c r="C51" s="3">
         <v>3191</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <f>6573-C51</f>
         <v>3382</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="3">
         <f>9768-SUM(C51:D51)</f>
         <v>3195</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="3">
         <f>12961-SUM(C51:E51)</f>
         <v>3193</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="3">
         <v>3745</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="3">
         <f>7548-G51</f>
         <v>3803</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="3">
         <f>11422-SUM(G51:H51)</f>
         <v>3874</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="3">
         <f>15376-SUM(G51:I51)</f>
         <v>3954</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="3">
         <v>4504</v>
       </c>
-      <c r="L51" s="2">
+      <c r="L51" s="3">
         <f>9286-K51</f>
         <v>4782</v>
       </c>
-      <c r="M51" s="11">
+      <c r="M51" s="3">
         <f>14262-SUM(K51:L51)</f>
         <v>4976</v>
       </c>
-      <c r="N51" s="2">
+      <c r="N51" s="3">
         <f>19362-SUM(K51:M51)</f>
         <v>5100</v>
       </c>
-      <c r="O51" s="2">
+      <c r="O51" s="3">
         <v>5284</v>
       </c>
-      <c r="P51" s="2">
+      <c r="P51" s="3">
         <f>11058-O51</f>
         <v>5774</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51" s="3">
         <f>16801-SUM(O51:P51)</f>
         <v>5743</v>
       </c>
-      <c r="R51" s="2">
+      <c r="R51" s="3">
         <f>22460-SUM(O51:Q51)</f>
         <v>5659</v>
       </c>
-      <c r="S51" s="2">
+      <c r="S51" s="3">
         <v>5264</v>
       </c>
-      <c r="T51" s="2">
+      <c r="T51" s="3">
         <f>11129-S51</f>
         <v>5865</v>
       </c>
-      <c r="U51" s="2">
+      <c r="U51" s="3">
         <f>16975-SUM(S51:T51)</f>
         <v>5846</v>
       </c>
-      <c r="V51" s="2">
+      <c r="V51" s="3">
         <f>22785-SUM(S51:U51)</f>
         <v>5810</v>
       </c>
-      <c r="W51" s="2">
+      <c r="W51" s="3">
         <v>5516</v>
       </c>
-      <c r="AI51" s="2"/>
-      <c r="AJ51" s="2"/>
-      <c r="AK51" s="2"/>
-      <c r="AL51" s="2"/>
-      <c r="AM51" s="2"/>
+      <c r="AI51" s="3"/>
+      <c r="AJ51" s="3"/>
+      <c r="AK51" s="3"/>
+      <c r="AL51" s="3"/>
+      <c r="AM51" s="3"/>
     </row>
     <row r="52" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="2">
+        <v>48</v>
+      </c>
+      <c r="C52" s="3">
         <v>175</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <f>-416-C52</f>
         <v>-591</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="3">
         <f>-280-SUM(C52:D52)</f>
         <v>136</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="3">
         <f>1390-SUM(C52:E52)</f>
         <v>1670</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="3">
         <f>1479-G52</f>
         <v>379</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I52" s="3">
         <f>192-SUM(G52:H52)</f>
         <v>-1287</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="3">
         <f>1808-SUM(G52:I52)</f>
         <v>1616</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="3">
         <v>-2090</v>
       </c>
-      <c r="L52" s="2">
+      <c r="L52" s="3">
         <f>-4237-K52</f>
         <v>-2147</v>
       </c>
-      <c r="M52" s="2">
+      <c r="M52" s="3">
         <f>-6157-SUM(K52:L52)</f>
         <v>-1920</v>
       </c>
-      <c r="N52" s="2">
+      <c r="N52" s="3">
         <f>-8081-SUM(K52:M52)</f>
         <v>-1924</v>
       </c>
-      <c r="O52" s="2">
+      <c r="O52" s="3">
         <v>-1854</v>
       </c>
-      <c r="P52" s="2">
+      <c r="P52" s="3">
         <f>-4269-O52</f>
         <v>-2415</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52" s="3">
         <f>-6093-SUM(O52:P52)</f>
         <v>-1824</v>
       </c>
-      <c r="R52" s="2">
+      <c r="R52" s="3">
         <f>-7763-SUM(O52:Q52)</f>
         <v>-1670</v>
       </c>
-      <c r="S52" s="2">
+      <c r="S52" s="3">
         <v>419</v>
       </c>
-      <c r="T52" s="2">
+      <c r="T52" s="3">
         <f>-2738-S52</f>
         <v>-3157</v>
       </c>
-      <c r="U52" s="2">
+      <c r="U52" s="3">
         <f>-3809-SUM(S52:T52)</f>
         <v>-1071</v>
       </c>
-      <c r="V52" s="2">
+      <c r="V52" s="3">
         <f>-5257-SUM(S52:U52)</f>
         <v>-1448</v>
       </c>
-      <c r="W52" s="2">
+      <c r="W52" s="3">
         <v>-1152</v>
       </c>
-      <c r="AI52" s="2"/>
-      <c r="AJ52" s="2"/>
-      <c r="AK52" s="2"/>
-      <c r="AL52" s="2"/>
-      <c r="AM52" s="2"/>
+      <c r="AI52" s="3"/>
+      <c r="AJ52" s="3"/>
+      <c r="AK52" s="3"/>
+      <c r="AL52" s="3"/>
+      <c r="AM52" s="3"/>
     </row>
     <row r="53" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="2">
+        <v>67</v>
+      </c>
+      <c r="C53" s="3">
         <v>802</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="3">
         <f>-1040-ABS(C53)</f>
         <v>-1842</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="3">
         <f>-3055-SUM(C53:D53)</f>
         <v>-2015</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="3">
         <f>-6317-SUM(C53:E53)</f>
         <v>-3262</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G53" s="3">
         <v>-4751</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="3">
         <f>7634-SUM(G53)</f>
         <v>12385</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I53" s="3">
         <f>-9792-SUM(G53:H53)</f>
         <v>-17426</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="3">
         <f>-12270-SUM(G53:I53)</f>
         <v>-2478</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53" s="3">
         <v>1437</v>
       </c>
-      <c r="L53" s="2">
+      <c r="L53" s="3">
         <v>2478</v>
       </c>
-      <c r="M53" s="2">
+      <c r="M53" s="3">
         <v>3856</v>
       </c>
-      <c r="N53" s="2">
+      <c r="N53" s="3">
         <v>5519</v>
       </c>
-      <c r="O53" s="2">
+      <c r="O53" s="3">
         <v>-84</v>
       </c>
-      <c r="P53" s="2">
+      <c r="P53" s="3">
         <f>425-O53</f>
         <v>509</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53" s="3">
         <f>1294-SUM(O53:P53)</f>
         <v>869</v>
       </c>
-      <c r="R53" s="2">
+      <c r="R53" s="3">
         <f>823-SUM(O53:Q53)</f>
         <v>-471</v>
       </c>
-      <c r="S53" s="2">
+      <c r="S53" s="3">
         <v>-1781</v>
       </c>
-      <c r="T53" s="2">
+      <c r="T53" s="3">
         <f>-757-S53</f>
         <v>1024</v>
       </c>
-      <c r="U53" s="2">
+      <c r="U53" s="3">
         <f>-2738-SUM(S53:T53)</f>
         <v>-1981</v>
       </c>
-      <c r="V53" s="2">
+      <c r="V53" s="3">
         <f>-2671-SUM(S53:U53)</f>
         <v>67</v>
       </c>
-      <c r="W53" s="2">
+      <c r="W53" s="3">
         <v>-9960</v>
       </c>
-      <c r="AI53" s="2"/>
-      <c r="AJ53" s="2"/>
-      <c r="AK53" s="2"/>
-      <c r="AL53" s="2"/>
-      <c r="AM53" s="2"/>
+      <c r="AI53" s="3"/>
+      <c r="AJ53" s="3"/>
+      <c r="AK53" s="3"/>
+      <c r="AL53" s="3"/>
+      <c r="AM53" s="3"/>
     </row>
     <row r="54" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="3">
         <v>297</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>669</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="3">
         <v>875</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="3">
         <v>1267</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G54" s="3">
         <v>-255</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="3">
         <v>-263</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I54" s="3">
         <v>-199</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="3">
         <v>-213</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K54" s="3">
         <v>140</v>
       </c>
-      <c r="L54" s="2">
+      <c r="L54" s="3">
         <v>202</v>
       </c>
-      <c r="M54" s="2">
+      <c r="M54" s="3">
         <v>369</v>
       </c>
-      <c r="N54" s="2">
+      <c r="N54" s="3">
         <v>1030</v>
       </c>
-      <c r="O54" s="2">
+      <c r="O54" s="3">
         <v>553</v>
       </c>
-      <c r="P54" s="2">
+      <c r="P54" s="3">
         <f>650-O54</f>
         <v>97</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54" s="3">
         <f>912-SUM(O54:P54)</f>
         <v>262</v>
       </c>
-      <c r="R54" s="2">
+      <c r="R54" s="3">
         <f>4330-SUM(O54:Q54)</f>
         <v>3418</v>
       </c>
-      <c r="S54" s="2">
+      <c r="S54" s="3">
         <v>334</v>
       </c>
-      <c r="T54" s="2">
+      <c r="T54" s="3">
         <f>1185-S54</f>
         <v>851</v>
       </c>
-      <c r="U54" s="2">
+      <c r="U54" s="3">
         <f>2592-SUM(S54:T54)</f>
         <v>1407</v>
       </c>
-      <c r="V54" s="2">
+      <c r="V54" s="3">
         <f>3419-SUM(S54:U54)</f>
         <v>827</v>
       </c>
-      <c r="W54" s="2">
+      <c r="W54" s="3">
         <v>481</v>
       </c>
-      <c r="AI54" s="2"/>
-      <c r="AJ54" s="2"/>
-      <c r="AK54" s="2"/>
-      <c r="AL54" s="2"/>
-      <c r="AM54" s="2"/>
+      <c r="AI54" s="3"/>
+      <c r="AJ54" s="3"/>
+      <c r="AK54" s="3"/>
+      <c r="AL54" s="3"/>
+      <c r="AM54" s="3"/>
     </row>
     <row r="55" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="2">
+        <v>68</v>
+      </c>
+      <c r="C55" s="3">
         <f>2602-245-115-835-3531-871+37</f>
         <v>-2958</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
         <f>2522+538-358-689-2099-692+148</f>
         <v>-630</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="3">
         <f>-1079+469-592-269+891+277+428</f>
         <v>125</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="3">
         <f>-6524+1209-1330+694+5504+1639+635-SUM(C55:E55)</f>
         <v>5290</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G55" s="3">
         <f>2794+785+7-962-3530-444+137</f>
         <v>-1213</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="3">
         <f>-867-297-192-112+201+29+134</f>
         <v>-1104</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I55" s="3">
         <f>-3276+2744-1447-874+2763+386+406</f>
         <v>702</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="3">
         <f>-9095-625-1846+283+7304+1682+774</f>
         <v>-1523</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K55" s="3">
         <f>4364+3820-776-2373-3216-828-94</f>
         <v>897</v>
       </c>
-      <c r="L55" s="2">
+      <c r="L55" s="3">
         <f>2395-253-1621-1172-1719-942-8</f>
         <v>-3320</v>
       </c>
-      <c r="M55" s="2">
+      <c r="M55" s="3">
         <f>2298-862-4268+735+491-1022+104</f>
         <v>-2524</v>
       </c>
-      <c r="N55" s="2">
+      <c r="N55" s="3">
         <f>-2317+584-5046+707+3915-445+367</f>
         <v>-2235</v>
       </c>
-      <c r="O55" s="2">
+      <c r="O55" s="3">
         <f>4454+4069-746-1105-4496-602-201</f>
         <v>1373</v>
       </c>
-      <c r="P55" s="2">
+      <c r="P55" s="3">
         <f>1506+8520-1259+14-4037-418-17-O55</f>
         <v>2936</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55" s="3">
         <f>-1315+10392-2883+237-380-315+690-SUM(O55:P55)</f>
         <v>2117</v>
       </c>
-      <c r="R55" s="2">
+      <c r="R55" s="3">
         <f>-7833+523-2143+664+3937+482+525-SUM(O55:Q55)</f>
         <v>-10271</v>
       </c>
-      <c r="S55" s="2">
+      <c r="S55" s="3">
         <f>3167+3011-1000-2124-5054-322-141</f>
         <v>-2463</v>
       </c>
-      <c r="T55" s="2">
+      <c r="T55" s="3">
         <f>110-889-1532-563-5176+97+220-S55</f>
         <v>-5270</v>
       </c>
-      <c r="U55" s="2">
+      <c r="U55" s="3">
         <f>-1321-2797-2334-42-6366+478+860-SUM(S55:T55)</f>
         <v>-3789</v>
       </c>
-      <c r="V55" s="2">
+      <c r="V55" s="3">
         <f>-5891-2418-1397+359-1161+1059+1043-SUM(S55:U55)</f>
         <v>3116</v>
       </c>
-      <c r="W55" s="2">
+      <c r="W55" s="3">
         <f>1638+7197-1288-880-5045+116+500</f>
         <v>2238</v>
       </c>
-      <c r="AI55" s="2"/>
-      <c r="AJ55" s="2"/>
-      <c r="AK55" s="2"/>
-      <c r="AL55" s="2"/>
-      <c r="AM55" s="2"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
     <row r="56" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="2">
+        <v>69</v>
+      </c>
+      <c r="C56" s="3">
         <f t="shared" ref="C56:J56" si="58">SUM(C48:C55)</f>
         <v>11451</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
         <f t="shared" si="58"/>
         <v>11333</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="3">
         <f t="shared" si="58"/>
         <v>17041</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="3">
         <f t="shared" si="58"/>
         <v>21184</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="3">
         <f t="shared" si="58"/>
         <v>19309</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="3">
         <f t="shared" si="58"/>
         <v>36670</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I56" s="3">
         <f t="shared" si="58"/>
         <v>7904</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="3">
         <f t="shared" si="58"/>
         <v>25407</v>
       </c>
-      <c r="K56" s="2">
+      <c r="K56" s="3">
         <f t="shared" ref="K56:U56" si="59">SUM(K48:K55)</f>
         <v>25106</v>
       </c>
-      <c r="L56" s="2">
+      <c r="L56" s="3">
         <f t="shared" si="59"/>
         <v>21896</v>
       </c>
-      <c r="M56" s="2">
+      <c r="M56" s="3">
         <f t="shared" si="59"/>
         <v>22713</v>
       </c>
-      <c r="N56" s="2">
+      <c r="N56" s="3">
         <f>SUM(N48:N55)</f>
         <v>25315</v>
       </c>
-      <c r="O56" s="2">
+      <c r="O56" s="3">
         <f>SUM(O48:O55)</f>
         <v>23509</v>
       </c>
-      <c r="P56" s="2">
+      <c r="P56" s="3">
         <f>SUM(P48:P55)</f>
         <v>28666</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56" s="3">
         <f t="shared" si="59"/>
         <v>30656</v>
       </c>
-      <c r="R56" s="2">
+      <c r="R56" s="3">
         <f>SUM(R48:R55)</f>
         <v>19288</v>
       </c>
-      <c r="S56" s="2">
+      <c r="S56" s="3">
         <f>SUM(S48:S55)</f>
         <v>28848</v>
       </c>
-      <c r="T56" s="2">
+      <c r="T56" s="3">
         <f t="shared" si="59"/>
         <v>26640</v>
       </c>
-      <c r="U56" s="2">
+      <c r="U56" s="3">
         <f t="shared" si="59"/>
         <v>30698</v>
       </c>
-      <c r="V56" s="2">
+      <c r="V56" s="3">
         <f>SUM(V48:V55)</f>
         <v>39113</v>
       </c>
-      <c r="W56" s="2">
+      <c r="W56" s="3">
         <f>SUM(W48:W55)</f>
         <v>36150</v>
       </c>
-      <c r="AI56" s="2"/>
-      <c r="AJ56" s="2"/>
-      <c r="AK56" s="2"/>
-      <c r="AL56" s="2"/>
-      <c r="AM56" s="2"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
     <row r="57" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
-      <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="2"/>
-      <c r="W57" s="2"/>
-      <c r="AI57" s="2"/>
-      <c r="AJ57" s="2"/>
-      <c r="AK57" s="2"/>
-      <c r="AL57" s="2"/>
-      <c r="AM57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="AI57" s="3"/>
+      <c r="AJ57" s="3"/>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="3"/>
+      <c r="AM57" s="3"/>
     </row>
     <row r="58" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C58" s="2">
+        <v>70</v>
+      </c>
+      <c r="C58" s="3">
         <v>-6005</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
         <f>-11396-C58</f>
         <v>-5391</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="3">
         <f>-16802-SUM(C58:D58)</f>
         <v>-5406</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="3">
         <f>-22281-SUM(C58:E58)</f>
         <v>-5479</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G58" s="3">
         <v>-5942</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="3">
         <f>-11438-G58</f>
         <v>-5496</v>
       </c>
-      <c r="I58" s="2">
+      <c r="I58" s="3">
         <f>-18257-SUM(G58:H58)</f>
         <v>-6819</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="3">
         <f>-24640-SUM(G58:I58)</f>
         <v>-6383</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K58" s="3">
         <v>-9786</v>
       </c>
-      <c r="L58" s="2">
+      <c r="L58" s="3">
         <f>-16614-K58</f>
         <v>-6828</v>
       </c>
-      <c r="M58" s="2">
+      <c r="M58" s="3">
         <f>-23890-SUM(K58:L58)</f>
         <v>-7276</v>
       </c>
-      <c r="N58" s="2">
+      <c r="N58" s="3">
         <f>-31485-SUM(K58:M58)</f>
         <v>-7595</v>
       </c>
-      <c r="O58" s="2">
+      <c r="O58" s="3">
         <v>-6289</v>
       </c>
-      <c r="P58" s="2">
+      <c r="P58" s="3">
         <f>-13177-O58</f>
         <v>-6888</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58" s="3">
         <f>-21232-SUM(O58:P58)</f>
         <v>-8055</v>
       </c>
-      <c r="R58" s="2">
+      <c r="R58" s="3">
         <f>-32251-SUM(O58:Q58)</f>
         <v>-11019</v>
       </c>
-      <c r="S58" s="2">
+      <c r="S58" s="3">
         <v>-12012</v>
       </c>
-      <c r="T58" s="2">
+      <c r="T58" s="3">
         <f>-25198-S58</f>
         <v>-13186</v>
       </c>
-      <c r="U58" s="2">
+      <c r="U58" s="3">
         <f>-38259-SUM(S58:T58)</f>
         <v>-13061</v>
       </c>
-      <c r="V58" s="2">
+      <c r="V58" s="3">
         <f>-52535-SUM(S58:U58)</f>
         <v>-14276</v>
       </c>
-      <c r="W58" s="2">
+      <c r="W58" s="3">
         <v>-17197</v>
       </c>
-      <c r="AI58" s="2"/>
-      <c r="AJ58" s="2"/>
-      <c r="AK58" s="2"/>
-      <c r="AL58" s="2"/>
-      <c r="AM58" s="2"/>
+      <c r="AI58" s="3"/>
+      <c r="AJ58" s="3"/>
+      <c r="AK58" s="3"/>
+      <c r="AL58" s="3"/>
+      <c r="AM58" s="3"/>
     </row>
     <row r="59" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" s="2">
+        <v>71</v>
+      </c>
+      <c r="C59" s="3">
         <f>-37563+41811-572+260</f>
         <v>3936</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <f>-64111+65874-1311+473</f>
         <v>925</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="3">
         <f>-104932+97751-1864+598</f>
         <v>-8447</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="3">
         <f>-136576+132906-7175+1023</f>
         <v>-9822</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G59" s="3">
         <f>-36426+39248-646+19</f>
         <v>2195</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="3">
         <f>-60609+60667-1412+256</f>
         <v>-1098</v>
       </c>
-      <c r="I59" s="2">
+      <c r="I59" s="3">
         <f>-95106+92126-2068+590</f>
         <v>-4458</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="3">
         <f>-135196+128294-2838+934</f>
         <v>-8806</v>
       </c>
-      <c r="K59" s="2">
+      <c r="K59" s="3">
         <f>-28462+29779-776+12</f>
         <v>553</v>
       </c>
-      <c r="L59" s="2">
+      <c r="L59" s="3">
         <f>-50199+55374-1264+125</f>
         <v>4036</v>
       </c>
-      <c r="M59" s="2">
+      <c r="M59" s="3">
         <f>-67253+84087-1628+131</f>
         <v>15337</v>
       </c>
-      <c r="N59" s="2">
+      <c r="N59" s="3">
         <f>-78874+97822-2531+150</f>
         <v>16567</v>
       </c>
-      <c r="O59" s="2">
+      <c r="O59" s="3">
         <f>-14227+18327-626+36</f>
         <v>3510</v>
       </c>
-      <c r="P59" s="2">
+      <c r="P59" s="3">
         <f>-35589+37049-1513+181-O59</f>
         <v>-3382</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59" s="3">
         <f>-49422+52642-2176+743-SUM(O59:P59)</f>
         <v>1659</v>
       </c>
-      <c r="R59" s="2">
+      <c r="R59" s="3">
         <f>-77858+86672-3027+947-SUM(O59:Q59)</f>
         <v>4947</v>
       </c>
-      <c r="S59" s="2">
+      <c r="S59" s="3">
         <f>-20684+24985-1206+313</f>
         <v>3408</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T59" s="3">
         <f>-43011+58577-2199+605-S59</f>
         <v>10564</v>
       </c>
-      <c r="U59" s="2">
+      <c r="U59" s="3">
         <f>-65034+81779-3234+732</f>
         <v>14243</v>
       </c>
-      <c r="V59" s="2">
+      <c r="V59" s="3">
         <f t="shared" ref="V59:W59" si="60">-86679-SUM(S59:U59)</f>
         <v>-114894</v>
       </c>
-      <c r="W59" s="2">
+      <c r="W59" s="3">
         <f t="shared" si="60"/>
         <v>3408</v>
       </c>
-      <c r="AI59" s="2"/>
-      <c r="AJ59" s="2"/>
-      <c r="AK59" s="2"/>
-      <c r="AL59" s="2"/>
-      <c r="AM59" s="2"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="3"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="3"/>
+      <c r="AM59" s="3"/>
     </row>
     <row r="60" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="2">
+        <v>72</v>
+      </c>
+      <c r="C60" s="3">
         <v>-190</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
         <v>-355</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="3">
         <v>-368</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="3">
         <f>-738-SUM(C60:E60)</f>
         <v>175</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G60" s="3">
         <v>-1666</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="3">
         <v>-1974</v>
       </c>
-      <c r="I60" s="2">
+      <c r="I60" s="3">
         <v>-2233</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="3">
         <v>-2618</v>
       </c>
-      <c r="K60" s="2">
+      <c r="K60" s="3">
         <v>-173</v>
       </c>
-      <c r="L60" s="2">
+      <c r="L60" s="3">
         <v>-1236</v>
       </c>
-      <c r="M60" s="2">
+      <c r="M60" s="3">
         <v>-6885</v>
       </c>
-      <c r="N60" s="2">
+      <c r="N60" s="3">
         <v>-6969</v>
       </c>
-      <c r="O60" s="2">
+      <c r="O60" s="3">
         <v>-42</v>
       </c>
-      <c r="P60" s="2">
+      <c r="P60" s="3">
         <f>-340-O60</f>
         <v>-298</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60" s="3">
         <f>-466-SUM(O60:P60)</f>
         <v>-126</v>
       </c>
-      <c r="R60" s="2">
+      <c r="R60" s="3">
         <f>-495-SUM(O60:Q60)</f>
         <v>-29</v>
       </c>
-      <c r="S60" s="2">
+      <c r="S60" s="3">
         <v>-61</v>
       </c>
-      <c r="T60" s="2">
+      <c r="T60" s="3">
         <f>-87-S60</f>
         <v>-26</v>
       </c>
-      <c r="U60" s="2">
+      <c r="U60" s="3">
         <f>-2840-SUM(S60:T60)</f>
         <v>-2753</v>
       </c>
-      <c r="V60" s="2">
+      <c r="V60" s="3">
         <f t="shared" ref="V60:W60" si="61">-2931-SUM(S60:U60)</f>
         <v>-91</v>
       </c>
-      <c r="W60" s="2">
+      <c r="W60" s="3">
         <f t="shared" si="61"/>
         <v>-61</v>
       </c>
-      <c r="AI60" s="2"/>
-      <c r="AJ60" s="2"/>
-      <c r="AK60" s="2"/>
-      <c r="AL60" s="2"/>
-      <c r="AM60" s="2"/>
+      <c r="AI60" s="3"/>
+      <c r="AJ60" s="3"/>
+      <c r="AK60" s="3"/>
+      <c r="AL60" s="3"/>
+      <c r="AM60" s="3"/>
     </row>
     <row r="61" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="3">
         <v>412</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="3">
         <v>531</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="3">
         <v>125</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="3">
         <f>-68-SUM(C61:E61)</f>
         <v>-1136</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G61" s="3">
         <v>30</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="3">
         <v>53</v>
       </c>
-      <c r="I61" s="2">
+      <c r="I61" s="3">
         <v>441</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="3">
         <f>541-SUM(G61:I61)</f>
         <v>17</v>
       </c>
-      <c r="K61" s="10">
+      <c r="K61" s="4">
         <v>355</v>
       </c>
-      <c r="L61" s="2">
+      <c r="L61" s="3">
         <v>576</v>
       </c>
-      <c r="M61" s="2">
+      <c r="M61" s="3">
         <v>1367</v>
       </c>
-      <c r="N61" s="2">
+      <c r="N61" s="3">
         <v>1589</v>
       </c>
-      <c r="O61" s="2">
+      <c r="O61" s="3">
         <v>-125</v>
       </c>
-      <c r="P61" s="2">
+      <c r="P61" s="3">
         <f>-357-O61</f>
         <v>-232</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61" s="3">
         <f>-985-SUM(O61:P61)</f>
         <v>-628</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R61" s="3">
         <f>-1051-SUM(Q61)</f>
         <v>-423</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S61" s="3">
         <v>101</v>
       </c>
-      <c r="T61" s="2">
+      <c r="T61" s="3">
         <f>-32-S61</f>
         <v>-133</v>
       </c>
-      <c r="U61" s="2">
+      <c r="U61" s="3">
         <f>-2500-SUM(S61:T61)</f>
         <v>-2468</v>
       </c>
-      <c r="V61" s="2">
+      <c r="V61" s="3">
         <f t="shared" ref="V61:W61" si="62">-2668-SUM(S61:U61)</f>
         <v>-168</v>
       </c>
-      <c r="W61" s="2">
+      <c r="W61" s="3">
         <f t="shared" si="62"/>
         <v>101</v>
       </c>
-      <c r="AI61" s="2"/>
-      <c r="AJ61" s="2"/>
-      <c r="AK61" s="2"/>
-      <c r="AL61" s="2"/>
-      <c r="AM61" s="2"/>
+      <c r="AI61" s="3"/>
+      <c r="AJ61" s="3"/>
+      <c r="AK61" s="3"/>
+      <c r="AL61" s="3"/>
+      <c r="AM61" s="3"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" s="2">
+        <v>73</v>
+      </c>
+      <c r="C62" s="3">
         <f t="shared" ref="C62:W62" si="63">SUM(C58:C61)</f>
         <v>-1847</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="3">
         <f t="shared" si="63"/>
         <v>-4290</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="3">
         <f t="shared" si="63"/>
         <v>-14096</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="3">
         <f t="shared" si="63"/>
         <v>-16262</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G62" s="3">
         <f t="shared" si="63"/>
         <v>-5383</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="3">
         <f>SUM(H58:H61)</f>
         <v>-8515</v>
       </c>
-      <c r="I62" s="2">
+      <c r="I62" s="3">
         <f>SUM(I58:I61)</f>
         <v>-13069</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="3">
         <f t="shared" si="63"/>
         <v>-17790</v>
       </c>
-      <c r="K62" s="2">
+      <c r="K62" s="3">
         <f t="shared" si="63"/>
         <v>-9051</v>
       </c>
-      <c r="L62" s="2">
+      <c r="L62" s="3">
         <f t="shared" si="63"/>
         <v>-3452</v>
       </c>
-      <c r="M62" s="2">
+      <c r="M62" s="3">
         <f t="shared" si="63"/>
         <v>2543</v>
       </c>
-      <c r="N62" s="2">
+      <c r="N62" s="3">
         <f t="shared" si="63"/>
         <v>3592</v>
       </c>
-      <c r="O62" s="2">
+      <c r="O62" s="3">
         <f t="shared" si="63"/>
         <v>-2946</v>
       </c>
-      <c r="P62" s="2">
+      <c r="P62" s="3">
         <f t="shared" si="63"/>
         <v>-10800</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62" s="3">
         <f t="shared" si="63"/>
         <v>-7150</v>
       </c>
-      <c r="R62" s="2">
+      <c r="R62" s="3">
         <f t="shared" si="63"/>
         <v>-6524</v>
       </c>
-      <c r="S62" s="2">
+      <c r="S62" s="3">
         <f t="shared" si="63"/>
         <v>-8564</v>
       </c>
-      <c r="T62" s="2">
+      <c r="T62" s="3">
         <f t="shared" si="63"/>
         <v>-2781</v>
       </c>
-      <c r="U62" s="2">
+      <c r="U62" s="3">
         <f t="shared" si="63"/>
         <v>-4039</v>
       </c>
-      <c r="V62" s="2">
+      <c r="V62" s="3">
         <f t="shared" si="63"/>
         <v>-129429</v>
       </c>
-      <c r="W62" s="2">
+      <c r="W62" s="3">
         <f t="shared" si="63"/>
         <v>-13749</v>
       </c>
-      <c r="AI62" s="2"/>
-      <c r="AJ62" s="2"/>
-      <c r="AK62" s="2"/>
-      <c r="AL62" s="2"/>
-      <c r="AM62" s="2"/>
+      <c r="AI62" s="3"/>
+      <c r="AJ62" s="3"/>
+      <c r="AK62" s="3"/>
+      <c r="AL62" s="3"/>
+      <c r="AM62" s="3"/>
     </row>
     <row r="63" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
-      <c r="AI63" s="2"/>
-      <c r="AJ63" s="2"/>
-      <c r="AK63" s="2"/>
-      <c r="AL63" s="2"/>
-      <c r="AM63" s="2"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="AI63" s="3"/>
+      <c r="AJ63" s="3"/>
+      <c r="AK63" s="3"/>
+      <c r="AL63" s="3"/>
+      <c r="AM63" s="3"/>
     </row>
     <row r="64" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="2">
+        <v>66</v>
+      </c>
+      <c r="C64" s="3">
         <v>-1241</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
         <v>-2716</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="3">
         <v>-4073</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="3">
         <v>-5720</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G64" s="3">
         <v>-2184</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="3">
         <v>-4637</v>
       </c>
-      <c r="I64" s="2">
+      <c r="I64" s="3">
         <v>-7239</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="3">
         <v>-10162</v>
       </c>
-      <c r="K64" s="2">
+      <c r="K64" s="3">
         <v>-2916</v>
       </c>
-      <c r="L64" s="2">
+      <c r="L64" s="3">
         <v>-5180</v>
       </c>
-      <c r="M64" s="2">
+      <c r="M64" s="3">
         <v>-7221</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="3">
         <v>-9300</v>
       </c>
-      <c r="O64" s="2">
+      <c r="O64" s="3">
         <v>-1989</v>
       </c>
-      <c r="P64" s="2">
+      <c r="P64" s="3">
         <f>-4725-O64</f>
         <v>-2736</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64" s="3">
         <f>-7157-SUM(O64:P64)</f>
         <v>-2432</v>
       </c>
-      <c r="R64" s="2">
+      <c r="R64" s="3">
         <f>-9837-SUM(O64:Q64)</f>
         <v>-2680</v>
       </c>
-      <c r="S64" s="2">
+      <c r="S64" s="3">
         <v>-2929</v>
       </c>
-      <c r="T64" s="2">
+      <c r="T64" s="3">
         <f>-6138-S64</f>
         <v>-3209</v>
       </c>
-      <c r="U64" s="2">
+      <c r="U64" s="3">
         <f>-9141-SUM(S64:T64)</f>
         <v>-3003</v>
       </c>
-      <c r="V64" s="2">
+      <c r="V64" s="3">
         <f t="shared" ref="V64:W64" si="64">-12190-SUM(S64:U64)</f>
         <v>-3049</v>
       </c>
-      <c r="W64" s="2">
+      <c r="W64" s="3">
         <f t="shared" si="64"/>
         <v>-2929</v>
       </c>
-      <c r="AI64" s="2"/>
-      <c r="AJ64" s="2"/>
-      <c r="AK64" s="2"/>
-      <c r="AL64" s="2"/>
-      <c r="AM64" s="2"/>
+      <c r="AI64" s="3"/>
+      <c r="AJ64" s="3"/>
+      <c r="AK64" s="3"/>
+      <c r="AL64" s="3"/>
+      <c r="AM64" s="3"/>
     </row>
     <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" s="2">
+        <v>74</v>
+      </c>
+      <c r="C65" s="3">
         <v>-8496</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="3">
         <v>-15348</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="3">
         <v>-23245</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="3">
         <v>31149</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G65" s="3">
         <v>-11395</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="3">
         <v>-24191</v>
       </c>
-      <c r="I65" s="2">
+      <c r="I65" s="3">
         <v>36801</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="3">
         <v>-50274</v>
       </c>
-      <c r="K65" s="2">
+      <c r="K65" s="3">
         <v>-13300</v>
       </c>
-      <c r="L65" s="2">
+      <c r="L65" s="3">
         <v>-28497</v>
       </c>
-      <c r="M65" s="2">
+      <c r="M65" s="3">
         <v>-43889</v>
       </c>
-      <c r="N65" s="2">
+      <c r="N65" s="3">
         <v>-59296</v>
       </c>
-      <c r="O65" s="2">
+      <c r="O65" s="3">
         <v>-14557</v>
       </c>
-      <c r="P65" s="2">
+      <c r="P65" s="3">
         <f>-29526-O65</f>
         <v>-14969</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65" s="3">
         <f>-45313-SUM(O65:P65)</f>
         <v>-15787</v>
       </c>
-      <c r="R65" s="2">
+      <c r="R65" s="3">
         <f>-61504-SUM(O65:Q65)</f>
         <v>-16191</v>
       </c>
-      <c r="S65" s="2">
+      <c r="S65" s="3">
         <v>-15696</v>
       </c>
-      <c r="T65" s="2">
+      <c r="T65" s="3">
         <f>-31380-S65</f>
         <v>-15684</v>
       </c>
-      <c r="U65" s="2">
+      <c r="U65" s="3">
         <f>-46671-SUM(S65:T65)</f>
         <v>-15291</v>
       </c>
-      <c r="V65" s="2">
+      <c r="V65" s="3">
         <f t="shared" ref="V65:W65" si="65">-62222-SUM(S65:U65)</f>
         <v>-15551</v>
       </c>
-      <c r="W65" s="2">
+      <c r="W65" s="3">
         <f t="shared" si="65"/>
         <v>-15696</v>
       </c>
-      <c r="AI65" s="2"/>
-      <c r="AJ65" s="2"/>
-      <c r="AK65" s="2"/>
-      <c r="AL65" s="2"/>
-      <c r="AM65" s="2"/>
+      <c r="AI65" s="3"/>
+      <c r="AJ65" s="3"/>
+      <c r="AK65" s="3"/>
+      <c r="AL65" s="3"/>
+      <c r="AM65" s="3"/>
     </row>
     <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C66" s="2">
+        <v>75</v>
+      </c>
+      <c r="C66" s="3">
         <v>0</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="3">
         <v>0</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="3">
         <v>0</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="3">
         <v>0</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G66" s="3">
         <v>0</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="3">
         <v>0</v>
       </c>
-      <c r="I66" s="2">
+      <c r="I66" s="3">
         <v>0</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="3">
         <v>0</v>
       </c>
-      <c r="K66" s="2">
+      <c r="K66" s="3">
         <v>0</v>
       </c>
-      <c r="L66" s="2">
+      <c r="L66" s="3">
         <v>0</v>
       </c>
-      <c r="M66" s="2">
+      <c r="M66" s="3">
         <v>0</v>
       </c>
-      <c r="N66" s="2">
+      <c r="N66" s="3">
         <v>0</v>
       </c>
-      <c r="O66" s="2">
+      <c r="O66" s="3">
         <v>0</v>
       </c>
-      <c r="P66" s="2">
+      <c r="P66" s="3">
         <v>0</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66" s="3">
         <v>0</v>
       </c>
-      <c r="R66" s="2">
+      <c r="R66" s="3">
         <v>0</v>
       </c>
-      <c r="S66" s="2">
+      <c r="S66" s="3">
         <v>0</v>
       </c>
-      <c r="T66" s="2">
+      <c r="T66" s="3">
         <v>-2466</v>
       </c>
-      <c r="U66" s="2">
+      <c r="U66" s="3">
         <f>-4921-T66</f>
         <v>-2455</v>
       </c>
-      <c r="V66" s="2">
+      <c r="V66" s="3">
         <f t="shared" ref="V66:W66" si="66">-7363-SUM(S66:U66)</f>
         <v>-2442</v>
       </c>
-      <c r="W66" s="2">
+      <c r="W66" s="3">
         <f t="shared" si="66"/>
         <v>0</v>
       </c>
-      <c r="AI66" s="2"/>
-      <c r="AJ66" s="2"/>
-      <c r="AK66" s="2"/>
-      <c r="AL66" s="2"/>
-      <c r="AM66" s="2"/>
+      <c r="AI66" s="3"/>
+      <c r="AJ66" s="3"/>
+      <c r="AK66" s="3"/>
+      <c r="AL66" s="3"/>
+      <c r="AM66" s="3"/>
     </row>
     <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="3">
         <f>1898-1947</f>
         <v>-49</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="3">
         <f>1898-1982</f>
         <v>-84</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="3">
         <f>11761-2043</f>
         <v>9718</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="3">
         <f>11761-2100</f>
         <v>9661</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G67" s="3">
         <f>900-937</f>
         <v>-37</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="3">
         <f>7599-8678</f>
         <v>-1079</v>
       </c>
-      <c r="I67" s="2">
+      <c r="I67" s="3">
         <f>13949-15070</f>
         <v>-1121</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="3">
         <f>20199-21435</f>
         <v>-1236</v>
       </c>
-      <c r="K67" s="2">
+      <c r="K67" s="3">
         <f>16422-16420</f>
         <v>2</v>
       </c>
-      <c r="L67" s="2">
+      <c r="L67" s="3">
         <f>29228-29582</f>
         <v>-354</v>
       </c>
-      <c r="M67" s="2">
+      <c r="M67" s="3">
         <f>44322-45350</f>
         <v>-1028</v>
       </c>
-      <c r="N67" s="2">
+      <c r="N67" s="3">
         <f>52872-54068</f>
         <v>-1196</v>
       </c>
-      <c r="O67" s="2">
+      <c r="O67" s="3">
         <f>6927-6952</f>
         <v>-25</v>
       </c>
-      <c r="P67" s="2">
+      <c r="P67" s="3">
         <f>8050-8207-O67</f>
         <v>-132</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67" s="3">
         <f>9298-9621-SUM(O67:P67)</f>
         <v>-166</v>
       </c>
-      <c r="R67" s="2">
+      <c r="R67" s="3">
         <f>10790-11550-SUM(O67:Q67)</f>
         <v>-437</v>
       </c>
-      <c r="S67" s="2">
+      <c r="S67" s="3">
         <f>1982-3079</f>
         <v>-1097</v>
       </c>
-      <c r="T67" s="2">
+      <c r="T67" s="3">
         <f>4875-5502-S67</f>
         <v>470</v>
       </c>
-      <c r="U67" s="2">
+      <c r="U67" s="3">
         <f>8694-8951-SUM(S67:T67)</f>
         <v>370</v>
       </c>
-      <c r="V67" s="2">
+      <c r="V67" s="3">
         <f t="shared" ref="V67:W67" si="67">13589-SUM(S67:U67)</f>
         <v>13846</v>
       </c>
-      <c r="W67" s="2">
+      <c r="W67" s="3">
         <f t="shared" si="67"/>
         <v>-1097</v>
       </c>
-      <c r="AI67" s="2"/>
-      <c r="AJ67" s="2"/>
-      <c r="AK67" s="2"/>
-      <c r="AL67" s="2"/>
-      <c r="AM67" s="2"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
     <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68" s="2">
+        <v>76</v>
+      </c>
+      <c r="C68" s="3">
         <v>1600</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="3">
         <v>2464</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="3">
         <v>2462</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="3">
         <v>2800</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G68" s="3">
         <v>10</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="3">
         <v>310</v>
       </c>
-      <c r="I68" s="2">
+      <c r="I68" s="3">
         <v>310</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="3">
         <v>310</v>
       </c>
-      <c r="K68" s="2">
+      <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="2">
+      <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="2">
+      <c r="M68" s="3">
         <v>10</v>
       </c>
-      <c r="N68" s="2">
+      <c r="N68" s="3">
         <v>35</v>
       </c>
-      <c r="O68" s="2">
+      <c r="O68" s="3">
         <v>3</v>
       </c>
-      <c r="P68" s="2">
+      <c r="P68" s="3">
         <f>5-O68</f>
         <v>2</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68" s="3">
         <f>8-SUM(O68:P68)</f>
         <v>3</v>
       </c>
-      <c r="R68" s="2">
+      <c r="R68" s="3">
         <f>8-SUM(O68:Q68)</f>
         <v>0</v>
       </c>
-      <c r="S68" s="2">
+      <c r="S68" s="3">
         <v>8</v>
       </c>
-      <c r="T68" s="2">
+      <c r="T68" s="3">
         <f>8-S68</f>
         <v>0</v>
       </c>
-      <c r="U68" s="2">
+      <c r="U68" s="3">
         <f>293-SUM(S68:T68)</f>
         <v>285</v>
       </c>
-      <c r="V68" s="2">
+      <c r="V68" s="3">
         <f t="shared" ref="V68:W68" si="68">1154-SUM(S68:U68)</f>
         <v>861</v>
       </c>
-      <c r="W68" s="2">
+      <c r="W68" s="3">
         <f t="shared" si="68"/>
         <v>8</v>
       </c>
-      <c r="AI68" s="2"/>
-      <c r="AJ68" s="2"/>
-      <c r="AK68" s="2"/>
-      <c r="AL68" s="2"/>
-      <c r="AM68" s="2"/>
+      <c r="AI68" s="3"/>
+      <c r="AJ68" s="3"/>
+      <c r="AK68" s="3"/>
+      <c r="AL68" s="3"/>
+      <c r="AM68" s="3"/>
     </row>
     <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C69" s="2">
+        <v>77</v>
+      </c>
+      <c r="C69" s="3">
         <f t="shared" ref="C69:W69" si="69">SUM(C64:C68)</f>
         <v>-8186</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="3">
         <f t="shared" si="69"/>
         <v>-15684</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="3">
         <f t="shared" si="69"/>
         <v>-15138</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="3">
         <f t="shared" si="69"/>
         <v>37890</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G69" s="3">
         <f t="shared" si="69"/>
         <v>-13606</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="3">
         <f t="shared" si="69"/>
         <v>-29597</v>
       </c>
-      <c r="I69" s="2">
+      <c r="I69" s="3">
         <f t="shared" si="69"/>
         <v>28751</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="3">
         <f t="shared" si="69"/>
         <v>-61362</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69" s="3">
         <f t="shared" si="69"/>
         <v>-16214</v>
       </c>
-      <c r="L69" s="2">
+      <c r="L69" s="3">
         <f t="shared" si="69"/>
         <v>-34031</v>
       </c>
-      <c r="M69" s="2">
+      <c r="M69" s="3">
         <f t="shared" si="69"/>
         <v>-52128</v>
       </c>
-      <c r="N69" s="2">
+      <c r="N69" s="3">
         <f>SUM(N64:N68)</f>
         <v>-69757</v>
       </c>
-      <c r="O69" s="2">
+      <c r="O69" s="3">
         <f t="shared" si="69"/>
         <v>-16568</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="3">
         <f t="shared" si="69"/>
         <v>-17835</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69" s="3">
         <f t="shared" si="69"/>
         <v>-18382</v>
       </c>
-      <c r="R69" s="2">
+      <c r="R69" s="3">
         <f>SUM(R64:R68)</f>
         <v>-19308</v>
       </c>
-      <c r="S69" s="2">
+      <c r="S69" s="3">
         <f>SUM(S64:S68)</f>
         <v>-19714</v>
       </c>
-      <c r="T69" s="2">
+      <c r="T69" s="3">
         <f t="shared" si="69"/>
         <v>-20889</v>
       </c>
-      <c r="U69" s="2">
+      <c r="U69" s="3">
         <f t="shared" si="69"/>
         <v>-20094</v>
       </c>
-      <c r="V69" s="2">
+      <c r="V69" s="3">
         <f t="shared" si="69"/>
         <v>-6335</v>
       </c>
-      <c r="W69" s="2">
+      <c r="W69" s="3">
         <f t="shared" si="69"/>
         <v>-19714</v>
       </c>
-      <c r="AI69" s="2"/>
-      <c r="AJ69" s="2"/>
-      <c r="AK69" s="2"/>
-      <c r="AL69" s="2"/>
-      <c r="AM69" s="2"/>
+      <c r="AI69" s="3"/>
+      <c r="AJ69" s="3"/>
+      <c r="AK69" s="3"/>
+      <c r="AL69" s="3"/>
+      <c r="AM69" s="3"/>
     </row>
     <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" s="2">
+        <v>78</v>
+      </c>
+      <c r="C70" s="3">
         <v>-272</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="3">
         <v>-221</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="3">
         <v>-186</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="3">
         <v>24</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="3">
         <v>-143</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="3">
         <v>40</v>
       </c>
-      <c r="I70" s="2">
+      <c r="I70" s="3">
         <v>-106</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="3">
         <v>-287</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70" s="3">
         <v>100</v>
       </c>
-      <c r="L70" s="2">
+      <c r="L70" s="3">
         <v>-268</v>
       </c>
-      <c r="M70" s="2">
+      <c r="M70" s="3">
         <v>-643</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="3">
         <v>-506</v>
       </c>
-      <c r="O70" s="2">
+      <c r="O70" s="3">
         <v>50</v>
       </c>
-      <c r="P70" s="2">
+      <c r="P70" s="3">
         <f>24-O70</f>
         <v>-26</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="3">
         <f>-327-SUM(O70:P70)</f>
         <v>-351</v>
       </c>
-      <c r="R70" s="2">
+      <c r="R70" s="3">
         <f>-421-SUM(O70:Q70)</f>
         <v>-94</v>
       </c>
-      <c r="S70" s="2">
+      <c r="S70" s="3">
         <f>-612-SUM(P70:R70)</f>
         <v>-141</v>
       </c>
-      <c r="T70" s="2">
+      <c r="T70" s="3">
         <f>-363-S70</f>
         <v>-222</v>
       </c>
-      <c r="U70" s="2">
+      <c r="U70" s="3">
         <f>-222-SUM(S70:T70)</f>
         <v>141</v>
       </c>
-      <c r="V70" s="2">
+      <c r="V70" s="3">
         <f t="shared" ref="V70:W70" si="70">-612-SUM(S70:U70)</f>
         <v>-390</v>
       </c>
-      <c r="W70" s="2">
+      <c r="W70" s="3">
         <f t="shared" si="70"/>
         <v>-141</v>
       </c>
-      <c r="AI70" s="2"/>
-      <c r="AJ70" s="2"/>
-      <c r="AK70" s="2"/>
-      <c r="AL70" s="2"/>
-      <c r="AM70" s="2"/>
+      <c r="AI70" s="3"/>
+      <c r="AJ70" s="3"/>
+      <c r="AK70" s="3"/>
+      <c r="AL70" s="3"/>
+      <c r="AM70" s="3"/>
     </row>
     <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B71" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" s="2">
+        <v>79</v>
+      </c>
+      <c r="C71" s="3">
         <f>+C70+C69+C62+C56</f>
         <v>1146</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="3">
         <f t="shared" ref="D71:W71" si="71">D62+D56+D69+D70</f>
         <v>-8862</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="3">
         <f t="shared" si="71"/>
         <v>-12379</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="3">
         <f t="shared" si="71"/>
         <v>42836</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="3">
         <f>G62+G56+G69+G70</f>
         <v>177</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="3">
         <f t="shared" si="71"/>
         <v>-1402</v>
       </c>
-      <c r="I71" s="2">
+      <c r="I71" s="3">
         <f t="shared" si="71"/>
         <v>23480</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="3">
         <f t="shared" si="71"/>
         <v>-54032</v>
       </c>
-      <c r="K71" s="2">
+      <c r="K71" s="3">
         <f t="shared" si="71"/>
         <v>-59</v>
       </c>
-      <c r="L71" s="2">
+      <c r="L71" s="3">
         <f t="shared" si="71"/>
         <v>-15855</v>
       </c>
-      <c r="M71" s="2">
+      <c r="M71" s="3">
         <f t="shared" si="71"/>
         <v>-27515</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="3">
         <f t="shared" si="71"/>
         <v>-41356</v>
       </c>
-      <c r="O71" s="2">
+      <c r="O71" s="3">
         <f t="shared" si="71"/>
         <v>4045</v>
       </c>
-      <c r="P71" s="2">
+      <c r="P71" s="3">
         <f>P62+P56+P69+P70</f>
         <v>5</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71" s="3">
         <f t="shared" si="71"/>
         <v>4773</v>
       </c>
-      <c r="R71" s="2">
+      <c r="R71" s="3">
         <f t="shared" si="71"/>
         <v>-6638</v>
       </c>
-      <c r="S71" s="2">
+      <c r="S71" s="3">
         <f>S62+S56+S69+S70</f>
         <v>429</v>
       </c>
-      <c r="T71" s="2">
+      <c r="T71" s="3">
         <f t="shared" si="71"/>
         <v>2748</v>
       </c>
-      <c r="U71" s="2">
+      <c r="U71" s="3">
         <f t="shared" si="71"/>
         <v>6706</v>
       </c>
-      <c r="V71" s="2">
+      <c r="V71" s="3">
         <f t="shared" si="71"/>
         <v>-97041</v>
       </c>
-      <c r="W71" s="2">
+      <c r="W71" s="3">
         <f t="shared" si="71"/>
         <v>2546</v>
       </c>
-      <c r="AI71" s="2"/>
-      <c r="AJ71" s="2"/>
-      <c r="AK71" s="2"/>
-      <c r="AL71" s="2"/>
-      <c r="AM71" s="2"/>
+      <c r="AI71" s="3"/>
+      <c r="AJ71" s="3"/>
+      <c r="AK71" s="3"/>
+      <c r="AL71" s="3"/>
+      <c r="AM71" s="3"/>
     </row>
     <row r="72" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-      <c r="AI72" s="2"/>
-      <c r="AJ72" s="2"/>
-      <c r="AK72" s="2"/>
-      <c r="AL72" s="2"/>
-      <c r="AM72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="AI72" s="3"/>
+      <c r="AJ72" s="3"/>
+      <c r="AK72" s="3"/>
+      <c r="AL72" s="3"/>
+      <c r="AM72" s="3"/>
     </row>
     <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2">
+        <v>80</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3">
         <v>25231</v>
       </c>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2">
+      <c r="H73" s="3"/>
+      <c r="I73" s="3">
         <v>32358</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73" s="3">
         <v>6383</v>
       </c>
-      <c r="K73" s="2">
+      <c r="K73" s="3">
         <f t="shared" ref="K73:V73" si="72">K58+K56</f>
         <v>15320</v>
       </c>
-      <c r="L73" s="2">
+      <c r="L73" s="3">
         <v>12594</v>
       </c>
-      <c r="M73" s="2">
+      <c r="M73" s="3">
         <v>16077</v>
       </c>
-      <c r="N73" s="2">
+      <c r="N73" s="3">
         <v>16019</v>
       </c>
-      <c r="O73" s="2">
+      <c r="O73" s="3">
         <f t="shared" si="72"/>
         <v>17220</v>
       </c>
-      <c r="P73" s="2">
+      <c r="P73" s="3">
         <f t="shared" si="72"/>
         <v>21778</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73" s="3">
         <f t="shared" si="72"/>
         <v>22601</v>
       </c>
-      <c r="R73" s="2">
+      <c r="R73" s="3">
         <v>7896</v>
       </c>
-      <c r="S73" s="2">
+      <c r="S73" s="3">
         <f t="shared" si="72"/>
         <v>16836</v>
       </c>
-      <c r="T73" s="2">
+      <c r="T73" s="3">
         <f t="shared" si="72"/>
         <v>13454</v>
       </c>
-      <c r="U73" s="2">
+      <c r="U73" s="3">
         <f t="shared" si="72"/>
         <v>17637</v>
       </c>
-      <c r="V73" s="2">
+      <c r="V73" s="3">
         <f t="shared" si="72"/>
         <v>24837</v>
       </c>
-      <c r="W73" s="2">
+      <c r="W73" s="3">
         <f>W58+W56</f>
         <v>18953</v>
       </c>
-      <c r="AI73" s="2"/>
-      <c r="AJ73" s="2"/>
-      <c r="AK73" s="2"/>
-      <c r="AL73" s="2"/>
-      <c r="AM73" s="2"/>
+      <c r="AI73" s="3"/>
+      <c r="AJ73" s="3"/>
+      <c r="AK73" s="3"/>
+      <c r="AL73" s="3"/>
+      <c r="AM73" s="3"/>
     </row>
     <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2">
+        <v>81</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3">
         <f>SUM(G73:J73)</f>
         <v>63972</v>
       </c>
-      <c r="K74" s="2">
+      <c r="K74" s="3">
         <f>SUM(H73:K73)</f>
         <v>54061</v>
       </c>
-      <c r="L74" s="2">
+      <c r="L74" s="3">
         <f t="shared" ref="L74:S74" si="73">SUM(I73:L73)</f>
         <v>66655</v>
       </c>
-      <c r="M74" s="2">
+      <c r="M74" s="3">
         <f t="shared" si="73"/>
         <v>50374</v>
       </c>
-      <c r="N74" s="2">
+      <c r="N74" s="3">
         <f t="shared" si="73"/>
         <v>60010</v>
       </c>
-      <c r="O74" s="2">
+      <c r="O74" s="3">
         <f>SUM(L73:O73)</f>
         <v>61910</v>
       </c>
-      <c r="P74" s="2">
+      <c r="P74" s="3">
         <f t="shared" si="73"/>
         <v>71094</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="Q74" s="3">
         <f>SUM(N73:Q73)</f>
         <v>77618</v>
       </c>
-      <c r="R74" s="2">
+      <c r="R74" s="3">
         <f t="shared" si="73"/>
         <v>69495</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74" s="3">
         <f t="shared" si="73"/>
         <v>69111</v>
       </c>
-      <c r="T74" s="2">
+      <c r="T74" s="3">
         <f>SUM(Q73:T73)</f>
         <v>60787</v>
       </c>
-      <c r="U74" s="2">
+      <c r="U74" s="3">
         <f>SUM(R73:U73)</f>
         <v>55823</v>
       </c>
-      <c r="V74" s="2">
+      <c r="V74" s="3">
         <f>SUM(S73:V73)</f>
         <v>72764</v>
       </c>
-      <c r="W74" s="2">
+      <c r="W74" s="3">
         <f>SUM(T73:W73)</f>
         <v>74881</v>
       </c>
-      <c r="AI74" s="2"/>
-      <c r="AJ74" s="2"/>
-      <c r="AK74" s="2"/>
-      <c r="AL74" s="2"/>
-      <c r="AM74" s="2"/>
+      <c r="AI74" s="3"/>
+      <c r="AJ74" s="3"/>
+      <c r="AK74" s="3"/>
+      <c r="AL74" s="3"/>
+      <c r="AM74" s="3"/>
     </row>
     <row r="75" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
     </row>
     <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-      <c r="T76" s="2"/>
-      <c r="U76" s="2"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
     </row>
     <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-      <c r="T77" s="2"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
     </row>
     <row r="78" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
     </row>
     <row r="79" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
     </row>
     <row r="80" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-      <c r="T80" s="2"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
